--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W407"/>
+  <dimension ref="A1:W408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30748,10 +30748,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>324.45</v>
+        <v>327.79</v>
       </c>
       <c r="C407" t="n">
-        <v>313.58</v>
+        <v>327.69</v>
       </c>
       <c r="D407" t="n">
         <v>331.89</v>
@@ -30760,19 +30760,19 @@
         <v>319.28</v>
       </c>
       <c r="F407" t="n">
-        <v>247.57</v>
+        <v>262.53</v>
       </c>
       <c r="G407" t="n">
-        <v>260.57</v>
+        <v>271.8</v>
       </c>
       <c r="H407" t="n">
         <v>318.62</v>
       </c>
       <c r="I407" t="n">
-        <v>256.04</v>
+        <v>266.8</v>
       </c>
       <c r="J407" t="n">
-        <v>256.62</v>
+        <v>266.4</v>
       </c>
       <c r="K407" t="n">
         <v>281.59</v>
@@ -30784,7 +30784,7 @@
         <v>321.93</v>
       </c>
       <c r="N407" t="n">
-        <v>315.5</v>
+        <v>317.33</v>
       </c>
       <c r="O407" t="n">
         <v>319.3</v>
@@ -30813,6 +30813,81 @@
       <c r="W407" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>329.13</v>
+      </c>
+      <c r="C408" t="n">
+        <v>328.02</v>
+      </c>
+      <c r="D408" t="n">
+        <v>317.26</v>
+      </c>
+      <c r="E408" t="n">
+        <v>310.2</v>
+      </c>
+      <c r="F408" t="n">
+        <v>271.09</v>
+      </c>
+      <c r="G408" t="n">
+        <v>280.06</v>
+      </c>
+      <c r="H408" t="n">
+        <v>320.17</v>
+      </c>
+      <c r="I408" t="n">
+        <v>271.92</v>
+      </c>
+      <c r="J408" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="K408" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="L408" t="n">
+        <v>284.59</v>
+      </c>
+      <c r="M408" t="n">
+        <v>319.99</v>
+      </c>
+      <c r="N408" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="O408" t="n">
+        <v>317.07</v>
+      </c>
+      <c r="P408" t="n">
+        <v>325.38</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>333.31</v>
+      </c>
+      <c r="R408" t="n">
+        <v>340.22</v>
+      </c>
+      <c r="S408" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="T408" t="n">
+        <v>351.96</v>
+      </c>
+      <c r="U408" t="n">
+        <v>337.65</v>
+      </c>
+      <c r="V408" t="n">
+        <v>326.23</v>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B443"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35260,6 +35335,16 @@
       </c>
       <c r="B443" t="n">
         <v>1.66</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -35428,28 +35513,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3706010729707867</v>
+        <v>-0.3660810659437113</v>
       </c>
       <c r="J2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02523230330399395</v>
+        <v>0.02474859103575544</v>
       </c>
       <c r="M2" t="n">
-        <v>11.77011920503127</v>
+        <v>11.7575539130082</v>
       </c>
       <c r="N2" t="n">
-        <v>249.7450926177557</v>
+        <v>249.2392786617412</v>
       </c>
       <c r="O2" t="n">
-        <v>15.80332536581322</v>
+        <v>15.78731385200602</v>
       </c>
       <c r="P2" t="n">
-        <v>333.3879495614763</v>
+        <v>333.3360513374107</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35506,28 +35591,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3822600837477968</v>
+        <v>-0.3734426707477422</v>
       </c>
       <c r="J3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008984826304958005</v>
+        <v>0.008625649835515947</v>
       </c>
       <c r="M3" t="n">
-        <v>18.50186171031374</v>
+        <v>18.42632571753911</v>
       </c>
       <c r="N3" t="n">
-        <v>758.6263200219506</v>
+        <v>756.4662887684982</v>
       </c>
       <c r="O3" t="n">
-        <v>27.54317193102404</v>
+        <v>27.50393224192676</v>
       </c>
       <c r="P3" t="n">
-        <v>334.9727060128546</v>
+        <v>334.8715902352546</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35584,28 +35669,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.017441255886607</v>
+        <v>-1.021497801162432</v>
       </c>
       <c r="J4" t="n">
+        <v>407</v>
+      </c>
+      <c r="K4" t="n">
         <v>406</v>
       </c>
-      <c r="K4" t="n">
-        <v>405</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03612813017197369</v>
+        <v>0.03658289278218785</v>
       </c>
       <c r="M4" t="n">
-        <v>23.41533458630869</v>
+        <v>23.39133065933529</v>
       </c>
       <c r="N4" t="n">
-        <v>1300.703979897231</v>
+        <v>1297.651099618427</v>
       </c>
       <c r="O4" t="n">
-        <v>36.06527387802886</v>
+        <v>36.0229246399904</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7281389609474</v>
+        <v>351.774714203159</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35662,28 +35747,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.323599594073225</v>
+        <v>-2.311882303787907</v>
       </c>
       <c r="J5" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K5" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1028278820117903</v>
+        <v>0.1023245286955849</v>
       </c>
       <c r="M5" t="n">
-        <v>35.30309934587105</v>
+        <v>35.23958241995349</v>
       </c>
       <c r="N5" t="n">
-        <v>2286.010291540474</v>
+        <v>2281.473756694148</v>
       </c>
       <c r="O5" t="n">
-        <v>47.81223997618678</v>
+        <v>47.76477527105249</v>
       </c>
       <c r="P5" t="n">
-        <v>348.4484978356155</v>
+        <v>348.3159551801226</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35740,28 +35825,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8707593622970101</v>
+        <v>-0.8771755854790357</v>
       </c>
       <c r="J6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K6" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01952478398389834</v>
+        <v>0.01992222852188563</v>
       </c>
       <c r="M6" t="n">
-        <v>32.3689124196985</v>
+        <v>32.32763925596146</v>
       </c>
       <c r="N6" t="n">
-        <v>1823.974685125711</v>
+        <v>1817.983857312663</v>
       </c>
       <c r="O6" t="n">
-        <v>42.70801663769592</v>
+        <v>42.63782191098254</v>
       </c>
       <c r="P6" t="n">
-        <v>321.1527272294632</v>
+        <v>321.2263164800717</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35818,28 +35903,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.001373995152256</v>
+        <v>-1.006051492835054</v>
       </c>
       <c r="J7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K7" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06203670709737408</v>
+        <v>0.06296832047171719</v>
       </c>
       <c r="M7" t="n">
-        <v>20.10368572395402</v>
+        <v>20.08276576251851</v>
       </c>
       <c r="N7" t="n">
-        <v>717.1774078680804</v>
+        <v>714.4126808413999</v>
       </c>
       <c r="O7" t="n">
-        <v>26.78016818222172</v>
+        <v>26.72849941245112</v>
       </c>
       <c r="P7" t="n">
-        <v>326.1979922516485</v>
+        <v>326.2518699799444</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35896,28 +35981,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2017381973018562</v>
+        <v>-0.1943542002879087</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K8" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005436789824219135</v>
+        <v>0.005066493106725467</v>
       </c>
       <c r="M8" t="n">
-        <v>15.15193127189883</v>
+        <v>15.14151241600326</v>
       </c>
       <c r="N8" t="n">
-        <v>356.593808541961</v>
+        <v>356.2207775893474</v>
       </c>
       <c r="O8" t="n">
-        <v>18.88369160259617</v>
+        <v>18.87381195173215</v>
       </c>
       <c r="P8" t="n">
-        <v>311.0319246335513</v>
+        <v>310.9477854458846</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35974,28 +36059,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8385774323420079</v>
+        <v>-0.8380293568091359</v>
       </c>
       <c r="J9" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K9" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03614739765333164</v>
+        <v>0.03631441574152816</v>
       </c>
       <c r="M9" t="n">
-        <v>25.14540890195623</v>
+        <v>25.07907670065596</v>
       </c>
       <c r="N9" t="n">
-        <v>910.3791645352821</v>
+        <v>907.2173918127147</v>
       </c>
       <c r="O9" t="n">
-        <v>30.17249019446824</v>
+        <v>30.12004966484476</v>
       </c>
       <c r="P9" t="n">
-        <v>303.4798327747804</v>
+        <v>303.4738081623786</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36052,28 +36137,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7466689877521351</v>
+        <v>-0.7437306075478854</v>
       </c>
       <c r="J10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K10" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02316834296193704</v>
+        <v>0.02311833137259134</v>
       </c>
       <c r="M10" t="n">
-        <v>28.16312900551736</v>
+        <v>28.07901599829631</v>
       </c>
       <c r="N10" t="n">
-        <v>1126.872270454158</v>
+        <v>1123.454270806665</v>
       </c>
       <c r="O10" t="n">
-        <v>33.56891821989737</v>
+        <v>33.51796937176632</v>
       </c>
       <c r="P10" t="n">
-        <v>294.4228113422832</v>
+        <v>294.3895263633992</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36130,28 +36215,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3452348758798304</v>
+        <v>-0.3468400985673956</v>
       </c>
       <c r="J11" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K11" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01579400717321455</v>
+        <v>0.01601933819543955</v>
       </c>
       <c r="M11" t="n">
-        <v>15.66216387605556</v>
+        <v>15.6303551124717</v>
       </c>
       <c r="N11" t="n">
-        <v>355.7612698473021</v>
+        <v>354.893446873896</v>
       </c>
       <c r="O11" t="n">
-        <v>18.86163486676863</v>
+        <v>18.83861584283453</v>
       </c>
       <c r="P11" t="n">
-        <v>296.2251364788164</v>
+        <v>296.2434024391727</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36208,28 +36293,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3890156429150776</v>
+        <v>-0.3903432442271126</v>
       </c>
       <c r="J12" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K12" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01539399798074037</v>
+        <v>0.01557601387200791</v>
       </c>
       <c r="M12" t="n">
-        <v>18.09720761295823</v>
+        <v>18.05870442604891</v>
       </c>
       <c r="N12" t="n">
-        <v>468.1835677441919</v>
+        <v>467.0296289749318</v>
       </c>
       <c r="O12" t="n">
-        <v>21.63754994781507</v>
+        <v>21.61086830682497</v>
       </c>
       <c r="P12" t="n">
-        <v>297.3468593178339</v>
+        <v>297.3618773650221</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36286,28 +36371,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4404649882435865</v>
+        <v>0.4446216167299406</v>
       </c>
       <c r="J13" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K13" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04437759981497658</v>
+        <v>0.04536693089776422</v>
       </c>
       <c r="M13" t="n">
-        <v>11.48038553738556</v>
+        <v>11.47298302062416</v>
       </c>
       <c r="N13" t="n">
-        <v>198.9755587975424</v>
+        <v>198.647719698266</v>
       </c>
       <c r="O13" t="n">
-        <v>14.10586965761213</v>
+        <v>14.09424420457748</v>
       </c>
       <c r="P13" t="n">
-        <v>300.3480398396896</v>
+        <v>300.3006239684395</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36364,28 +36449,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.342998639339361</v>
+        <v>0.3455225478098618</v>
       </c>
       <c r="J14" t="n">
+        <v>407</v>
+      </c>
+      <c r="K14" t="n">
         <v>406</v>
       </c>
-      <c r="K14" t="n">
-        <v>405</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02393423186900312</v>
+        <v>0.02439298371738852</v>
       </c>
       <c r="M14" t="n">
-        <v>11.98345677052494</v>
+        <v>11.96551476956961</v>
       </c>
       <c r="N14" t="n">
-        <v>229.0128960061705</v>
+        <v>228.5228312008626</v>
       </c>
       <c r="O14" t="n">
-        <v>15.13317204046034</v>
+        <v>15.11697162797042</v>
       </c>
       <c r="P14" t="n">
-        <v>301.8659949600749</v>
+        <v>301.8372677803334</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36442,28 +36527,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1087085581412039</v>
+        <v>-0.09566864900512803</v>
       </c>
       <c r="J15" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K15" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001680838987489719</v>
+        <v>0.001302806804527656</v>
       </c>
       <c r="M15" t="n">
-        <v>14.28510730818877</v>
+        <v>14.30919893478564</v>
       </c>
       <c r="N15" t="n">
-        <v>336.5126807454395</v>
+        <v>337.2686129663236</v>
       </c>
       <c r="O15" t="n">
-        <v>18.34428196320149</v>
+        <v>18.36487443372058</v>
       </c>
       <c r="P15" t="n">
-        <v>294.4854302642804</v>
+        <v>294.3372076224462</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36520,28 +36605,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.02167978227827298</v>
+        <v>-0.0163902039897198</v>
       </c>
       <c r="J16" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K16" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001272880802497545</v>
+        <v>7.301933637948732e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>9.87699788670349</v>
+        <v>9.87622798835312</v>
       </c>
       <c r="N16" t="n">
-        <v>175.505956749602</v>
+        <v>175.3324123093654</v>
       </c>
       <c r="O16" t="n">
-        <v>13.24786612060984</v>
+        <v>13.24131459898772</v>
       </c>
       <c r="P16" t="n">
-        <v>315.6368430570154</v>
+        <v>315.576297723882</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36598,28 +36683,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01060853795580261</v>
+        <v>-0.006030540486783682</v>
       </c>
       <c r="J17" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K17" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L17" t="n">
-        <v>4.263525577608007e-05</v>
+        <v>1.382694026508258e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>8.421209070417531</v>
+        <v>8.425180285945871</v>
       </c>
       <c r="N17" t="n">
-        <v>125.7123993254657</v>
+        <v>125.5988739757758</v>
       </c>
       <c r="O17" t="n">
-        <v>11.21215408944533</v>
+        <v>11.20709034387498</v>
       </c>
       <c r="P17" t="n">
-        <v>324.6344171631044</v>
+        <v>324.5821946131972</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36676,28 +36761,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.07414569929564002</v>
+        <v>-0.06831617648238043</v>
       </c>
       <c r="J18" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K18" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002707157981556407</v>
+        <v>0.002303300245203532</v>
       </c>
       <c r="M18" t="n">
-        <v>7.37654519965281</v>
+        <v>7.387826253482705</v>
       </c>
       <c r="N18" t="n">
-        <v>96.3787707156464</v>
+        <v>96.45781623150256</v>
       </c>
       <c r="O18" t="n">
-        <v>9.817269004954809</v>
+        <v>9.821294020214575</v>
       </c>
       <c r="P18" t="n">
-        <v>330.7825348436583</v>
+        <v>330.7159018091654</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36754,28 +36839,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.163873754598937</v>
+        <v>-0.1584510205194382</v>
       </c>
       <c r="J19" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K19" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009738239576675634</v>
+        <v>0.009137301623994842</v>
       </c>
       <c r="M19" t="n">
-        <v>8.930822893037178</v>
+        <v>8.93265068578526</v>
       </c>
       <c r="N19" t="n">
-        <v>130.059715021798</v>
+        <v>130.0142520627691</v>
       </c>
       <c r="O19" t="n">
-        <v>11.40437262727757</v>
+        <v>11.40237922815976</v>
       </c>
       <c r="P19" t="n">
-        <v>345.2878290780009</v>
+        <v>345.2259703716525</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36832,28 +36917,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1304690697234993</v>
+        <v>0.1342709069400005</v>
       </c>
       <c r="J20" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K20" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006084746563908894</v>
+        <v>0.006468448464616139</v>
       </c>
       <c r="M20" t="n">
-        <v>8.554287164650962</v>
+        <v>8.550047526234669</v>
       </c>
       <c r="N20" t="n">
-        <v>132.4269658633559</v>
+        <v>132.2363180670817</v>
       </c>
       <c r="O20" t="n">
-        <v>11.50769159577002</v>
+        <v>11.49940511796509</v>
       </c>
       <c r="P20" t="n">
-        <v>341.1149459663484</v>
+        <v>341.0715773024029</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36910,28 +36995,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.327070400478382</v>
+        <v>-0.3280289994542201</v>
       </c>
       <c r="J21" t="n">
+        <v>407</v>
+      </c>
+      <c r="K21" t="n">
         <v>406</v>
       </c>
-      <c r="K21" t="n">
-        <v>405</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03184915374904873</v>
+        <v>0.03218718378268537</v>
       </c>
       <c r="M21" t="n">
-        <v>9.243510557935362</v>
+        <v>9.225842270520863</v>
       </c>
       <c r="N21" t="n">
-        <v>154.5893813934126</v>
+        <v>154.2171705078271</v>
       </c>
       <c r="O21" t="n">
-        <v>12.43339782173049</v>
+        <v>12.41842061245419</v>
       </c>
       <c r="P21" t="n">
-        <v>348.0763660746071</v>
+        <v>348.0873207684767</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36988,28 +37073,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09269215716934474</v>
+        <v>-0.097036420616433</v>
       </c>
       <c r="J22" t="n">
+        <v>407</v>
+      </c>
+      <c r="K22" t="n">
         <v>406</v>
       </c>
-      <c r="K22" t="n">
-        <v>405</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.002257315990191855</v>
+        <v>0.002483550232972531</v>
       </c>
       <c r="M22" t="n">
-        <v>9.595467878990668</v>
+        <v>9.59720313726412</v>
       </c>
       <c r="N22" t="n">
-        <v>180.5361657039467</v>
+        <v>180.2671187040706</v>
       </c>
       <c r="O22" t="n">
-        <v>13.43637472326322</v>
+        <v>13.42635910081622</v>
       </c>
       <c r="P22" t="n">
-        <v>337.1342393850462</v>
+        <v>337.1838848336135</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37047,7 +37132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W407"/>
+  <dimension ref="A1:W408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84196,12 +84281,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>-37.685442543293995,174.81196189801355</t>
+          <t>-37.68545370505989,174.81192672980544</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>-37.68474284490385,174.81175337137998</t>
+          <t>-37.68478999813861,174.81160480272985</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -84216,12 +84301,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>-37.68253209925231,174.81147944915384</t>
+          <t>-37.68258209303948,174.8113219352313</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>-37.6819121479478,174.81101958656348</t>
+          <t>-37.68194967636535,174.81090134663177</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -84231,12 +84316,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>-37.680574487858166,174.8104268922325</t>
+          <t>-37.68060989910242,174.8103133307011</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>-37.67991293582748,174.8101059846831</t>
+          <t>-37.679944918816254,174.8100026671409</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -84256,7 +84341,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>-37.677443136340756,174.80822072021445</t>
+          <t>-37.67744912064969,174.80820138830353</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -84302,6 +84387,123 @@
       <c r="W407" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-37.68545818313075,174.81191262040153</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-37.684791100940636,174.81160132805317</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-37.684091764399945,174.81139164264215</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-37.683404786920995,174.81114299753258</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-37.6826106990178,174.81123180684563</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-37.68197727956205,174.81081437755614</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-37.681448489010435,174.81006936153372</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-37.680626749025,174.810259293948</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-37.67995963488567,174.80995512836364</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-37.67933722396122,174.80949986731028</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>-37.67867324242643,174.80917887707864</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>-37.67812341572659,174.80848909923668</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>-37.67743803496023,174.8082371998737</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>-37.676788641152704,174.80789111836708</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>-37.67615022648729,174.8075200836112</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>-37.67549570282515,174.80717530074108</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>-37.674834114615535,174.80683984962866</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>-37.67418468232371,174.80645609183878</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>-37.67350403415808,174.80619100801584</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>-37.67278015894117,174.8060402368959</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>-37.67208427750877,174.80576278430829</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W408"/>
+  <dimension ref="A1:W409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30888,6 +30888,81 @@
       <c r="W408" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>337.14</v>
+      </c>
+      <c r="C409" t="n">
+        <v>329.43</v>
+      </c>
+      <c r="D409" t="n">
+        <v>320.25</v>
+      </c>
+      <c r="E409" t="n">
+        <v>313.32</v>
+      </c>
+      <c r="F409" t="n">
+        <v>287.91</v>
+      </c>
+      <c r="G409" t="n">
+        <v>293.76</v>
+      </c>
+      <c r="H409" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="I409" t="n">
+        <v>283.16</v>
+      </c>
+      <c r="J409" t="n">
+        <v>280.85</v>
+      </c>
+      <c r="K409" t="n">
+        <v>290.26</v>
+      </c>
+      <c r="L409" t="n">
+        <v>293.56</v>
+      </c>
+      <c r="M409" t="n">
+        <v>316.46</v>
+      </c>
+      <c r="N409" t="n">
+        <v>311.16</v>
+      </c>
+      <c r="O409" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="P409" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="R409" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="S409" t="n">
+        <v>350.37</v>
+      </c>
+      <c r="T409" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="U409" t="n">
+        <v>338.66</v>
+      </c>
+      <c r="V409" t="n">
+        <v>326.41</v>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30902,7 +30977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B444"/>
+  <dimension ref="A1:B445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35345,6 +35420,16 @@
       </c>
       <c r="B444" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -35513,28 +35598,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3660810659437113</v>
+        <v>-0.3591974606693145</v>
       </c>
       <c r="J2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K2" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02474859103575544</v>
+        <v>0.02392662949472057</v>
       </c>
       <c r="M2" t="n">
-        <v>11.7575539130082</v>
+        <v>11.75352347755119</v>
       </c>
       <c r="N2" t="n">
-        <v>249.2392786617412</v>
+        <v>249.063382240696</v>
       </c>
       <c r="O2" t="n">
-        <v>15.78731385200602</v>
+        <v>15.78174205342034</v>
       </c>
       <c r="P2" t="n">
-        <v>333.3360513374107</v>
+        <v>333.2568584516781</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35591,28 +35676,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3734426707477422</v>
+        <v>-0.3712155316783862</v>
       </c>
       <c r="J3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K3" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008625649835515947</v>
+        <v>0.008566693976200246</v>
       </c>
       <c r="M3" t="n">
-        <v>18.42632571753911</v>
+        <v>18.38762600886922</v>
       </c>
       <c r="N3" t="n">
-        <v>756.4662887684982</v>
+        <v>754.6489203593459</v>
       </c>
       <c r="O3" t="n">
-        <v>27.50393224192676</v>
+        <v>27.47087403704778</v>
       </c>
       <c r="P3" t="n">
-        <v>334.8715902352546</v>
+        <v>334.845967968608</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35669,28 +35754,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.021497801162432</v>
+        <v>-1.023959025977997</v>
       </c>
       <c r="J4" t="n">
+        <v>408</v>
+      </c>
+      <c r="K4" t="n">
         <v>407</v>
       </c>
-      <c r="K4" t="n">
-        <v>406</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03658289278218785</v>
+        <v>0.03693270379064673</v>
       </c>
       <c r="M4" t="n">
-        <v>23.39133065933529</v>
+        <v>23.35428457714519</v>
       </c>
       <c r="N4" t="n">
-        <v>1297.651099618427</v>
+        <v>1294.518751612112</v>
       </c>
       <c r="O4" t="n">
-        <v>36.0229246399904</v>
+        <v>35.97942122397346</v>
       </c>
       <c r="P4" t="n">
-        <v>351.774714203159</v>
+        <v>351.8029986772949</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35747,28 +35832,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.311882303787907</v>
+        <v>-2.298676970490285</v>
       </c>
       <c r="J5" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K5" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1023245286955849</v>
+        <v>0.1016830374048084</v>
       </c>
       <c r="M5" t="n">
-        <v>35.23958241995349</v>
+        <v>35.18025139566122</v>
       </c>
       <c r="N5" t="n">
-        <v>2281.473756694148</v>
+        <v>2277.323255657352</v>
       </c>
       <c r="O5" t="n">
-        <v>47.76477527105249</v>
+        <v>47.72130819306353</v>
       </c>
       <c r="P5" t="n">
-        <v>348.3159551801226</v>
+        <v>348.1664383725914</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35825,28 +35910,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8771755854790357</v>
+        <v>-0.8824937698577415</v>
       </c>
       <c r="J6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K6" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01992222852188563</v>
+        <v>0.02025725304792236</v>
       </c>
       <c r="M6" t="n">
-        <v>32.32763925596146</v>
+        <v>32.28004286243486</v>
       </c>
       <c r="N6" t="n">
-        <v>1817.983857312663</v>
+        <v>1813.683613779166</v>
       </c>
       <c r="O6" t="n">
-        <v>42.63782191098254</v>
+        <v>42.58736448501088</v>
       </c>
       <c r="P6" t="n">
-        <v>321.2263164800717</v>
+        <v>321.2871612181829</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35903,28 +35988,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.006051492835054</v>
+        <v>-1.009310419713682</v>
       </c>
       <c r="J7" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K7" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06296832047171719</v>
+        <v>0.06365500588079509</v>
       </c>
       <c r="M7" t="n">
-        <v>20.08276576251851</v>
+        <v>20.05284858299877</v>
       </c>
       <c r="N7" t="n">
-        <v>714.4126808413999</v>
+        <v>712.6862357162308</v>
       </c>
       <c r="O7" t="n">
-        <v>26.72849941245112</v>
+        <v>26.69618391673669</v>
       </c>
       <c r="P7" t="n">
-        <v>326.2518699799444</v>
+        <v>326.2893093557642</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35981,28 +36066,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1943542002879087</v>
+        <v>-0.1869928616245634</v>
       </c>
       <c r="J8" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K8" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005066493106725467</v>
+        <v>0.004708721737944455</v>
       </c>
       <c r="M8" t="n">
-        <v>15.14151241600326</v>
+        <v>15.13105048675819</v>
       </c>
       <c r="N8" t="n">
-        <v>356.2207775893474</v>
+        <v>355.8519363288679</v>
       </c>
       <c r="O8" t="n">
-        <v>18.87381195173215</v>
+        <v>18.86403817661711</v>
       </c>
       <c r="P8" t="n">
-        <v>310.9477854458846</v>
+        <v>310.863825818031</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36059,28 +36144,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8380293568091359</v>
+        <v>-0.8372010569813176</v>
       </c>
       <c r="J9" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K9" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03631441574152816</v>
+        <v>0.03642395476126026</v>
       </c>
       <c r="M9" t="n">
-        <v>25.07907670065596</v>
+        <v>25.02001129874239</v>
       </c>
       <c r="N9" t="n">
-        <v>907.2173918127147</v>
+        <v>904.9387446935403</v>
       </c>
       <c r="O9" t="n">
-        <v>30.12004966484476</v>
+        <v>30.08219979811218</v>
       </c>
       <c r="P9" t="n">
-        <v>303.4738081623786</v>
+        <v>303.4644225132357</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36137,28 +36222,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7437306075478854</v>
+        <v>-0.7407004658331686</v>
       </c>
       <c r="J10" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K10" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02311833137259134</v>
+        <v>0.02304742202900156</v>
       </c>
       <c r="M10" t="n">
-        <v>28.07901599829631</v>
+        <v>28.02429470004603</v>
       </c>
       <c r="N10" t="n">
-        <v>1123.454270806665</v>
+        <v>1120.753120457462</v>
       </c>
       <c r="O10" t="n">
-        <v>33.51796937176632</v>
+        <v>33.47765105943758</v>
       </c>
       <c r="P10" t="n">
-        <v>294.3895263633992</v>
+        <v>294.355003545422</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36215,28 +36300,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3468400985673956</v>
+        <v>-0.3452406868590651</v>
       </c>
       <c r="J11" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K11" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01601933819543955</v>
+        <v>0.01595394507973447</v>
       </c>
       <c r="M11" t="n">
-        <v>15.6303551124717</v>
+        <v>15.59927747685287</v>
       </c>
       <c r="N11" t="n">
-        <v>354.893446873896</v>
+        <v>354.0300509784029</v>
       </c>
       <c r="O11" t="n">
-        <v>18.83861584283453</v>
+        <v>18.8156863010203</v>
       </c>
       <c r="P11" t="n">
-        <v>296.2434024391727</v>
+        <v>296.2251856179894</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36293,28 +36378,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3903432442271126</v>
+        <v>-0.3870593468908933</v>
       </c>
       <c r="J12" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K12" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01557601387200791</v>
+        <v>0.01539331519084108</v>
       </c>
       <c r="M12" t="n">
-        <v>18.05870442604891</v>
+        <v>18.02884438113055</v>
       </c>
       <c r="N12" t="n">
-        <v>467.0296289749318</v>
+        <v>465.9668985761314</v>
       </c>
       <c r="O12" t="n">
-        <v>21.61086830682497</v>
+        <v>21.5862664343821</v>
       </c>
       <c r="P12" t="n">
-        <v>297.3618773650221</v>
+        <v>297.3246944284198</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36371,28 +36456,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4446216167299406</v>
+        <v>0.4469228097285989</v>
       </c>
       <c r="J13" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K13" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04536693089776422</v>
+        <v>0.04602781542682799</v>
       </c>
       <c r="M13" t="n">
-        <v>11.47298302062416</v>
+        <v>11.45632982652871</v>
       </c>
       <c r="N13" t="n">
-        <v>198.647719698266</v>
+        <v>198.2106062451651</v>
       </c>
       <c r="O13" t="n">
-        <v>14.09424420457748</v>
+        <v>14.07872885757678</v>
       </c>
       <c r="P13" t="n">
-        <v>300.3006239684395</v>
+        <v>300.274349287634</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36449,28 +36534,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3455225478098618</v>
+        <v>0.3456620936753719</v>
       </c>
       <c r="J14" t="n">
+        <v>408</v>
+      </c>
+      <c r="K14" t="n">
         <v>407</v>
       </c>
-      <c r="K14" t="n">
-        <v>406</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02439298371738852</v>
+        <v>0.02453366727271344</v>
       </c>
       <c r="M14" t="n">
-        <v>11.96551476956961</v>
+        <v>11.93675086262677</v>
       </c>
       <c r="N14" t="n">
-        <v>228.5228312008626</v>
+        <v>227.9615332190341</v>
       </c>
       <c r="O14" t="n">
-        <v>15.11697162797042</v>
+        <v>15.09839505441006</v>
       </c>
       <c r="P14" t="n">
-        <v>301.8372677803334</v>
+        <v>301.8356763377291</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36527,28 +36612,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.09566864900512803</v>
+        <v>-0.08510101620080369</v>
       </c>
       <c r="J15" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K15" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001302806804527656</v>
+        <v>0.001033206563280875</v>
       </c>
       <c r="M15" t="n">
-        <v>14.30919893478564</v>
+        <v>14.32182179576306</v>
       </c>
       <c r="N15" t="n">
-        <v>337.2686129663236</v>
+        <v>337.488081248325</v>
       </c>
       <c r="O15" t="n">
-        <v>18.36487443372058</v>
+        <v>18.37084868067681</v>
       </c>
       <c r="P15" t="n">
-        <v>294.3372076224462</v>
+        <v>294.2169749941061</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36605,28 +36690,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0163902039897198</v>
+        <v>-0.01200113409874985</v>
       </c>
       <c r="J16" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K16" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L16" t="n">
-        <v>7.301933637948732e-05</v>
+        <v>3.930799647156036e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>9.87622798835312</v>
+        <v>9.871422269660711</v>
       </c>
       <c r="N16" t="n">
-        <v>175.3324123093654</v>
+        <v>175.0805881371561</v>
       </c>
       <c r="O16" t="n">
-        <v>13.24131459898772</v>
+        <v>13.23180215001555</v>
       </c>
       <c r="P16" t="n">
-        <v>315.576297723882</v>
+        <v>315.5260129490749</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36683,28 +36768,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.006030540486783682</v>
+        <v>-0.001661893880165067</v>
       </c>
       <c r="J17" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K17" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L17" t="n">
-        <v>1.382694026508258e-05</v>
+        <v>1.053928960992323e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>8.425180285945871</v>
+        <v>8.427957927888702</v>
       </c>
       <c r="N17" t="n">
-        <v>125.5988739757758</v>
+        <v>125.4703994595102</v>
       </c>
       <c r="O17" t="n">
-        <v>11.20709034387498</v>
+        <v>11.20135703651617</v>
       </c>
       <c r="P17" t="n">
-        <v>324.5821946131972</v>
+        <v>324.5323140533276</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36761,28 +36846,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.06831617648238043</v>
+        <v>-0.06328391850125234</v>
       </c>
       <c r="J18" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K18" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002303300245203532</v>
+        <v>0.001982254551312401</v>
       </c>
       <c r="M18" t="n">
-        <v>7.387826253482705</v>
+        <v>7.395247570028491</v>
       </c>
       <c r="N18" t="n">
-        <v>96.45781623150256</v>
+        <v>96.45842195196184</v>
       </c>
       <c r="O18" t="n">
-        <v>9.821294020214575</v>
+        <v>9.821324857266552</v>
       </c>
       <c r="P18" t="n">
-        <v>330.7159018091654</v>
+        <v>330.6583282340269</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36839,28 +36924,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1584510205194382</v>
+        <v>-0.1537261828604742</v>
       </c>
       <c r="J19" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K19" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009137301623994842</v>
+        <v>0.008634728660974034</v>
       </c>
       <c r="M19" t="n">
-        <v>8.93265068578526</v>
+        <v>8.931757780554177</v>
       </c>
       <c r="N19" t="n">
-        <v>130.0142520627691</v>
+        <v>129.9053965671612</v>
       </c>
       <c r="O19" t="n">
-        <v>11.40237922815976</v>
+        <v>11.39760486098554</v>
       </c>
       <c r="P19" t="n">
-        <v>345.2259703716525</v>
+        <v>345.1720228751062</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36917,28 +37002,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1342709069400005</v>
+        <v>0.1366068840210496</v>
       </c>
       <c r="J20" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K20" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006468448464616139</v>
+        <v>0.006725231976722035</v>
       </c>
       <c r="M20" t="n">
-        <v>8.550047526234669</v>
+        <v>8.539351811528791</v>
       </c>
       <c r="N20" t="n">
-        <v>132.2363180670817</v>
+        <v>131.9634935885416</v>
       </c>
       <c r="O20" t="n">
-        <v>11.49940511796509</v>
+        <v>11.48753644558056</v>
       </c>
       <c r="P20" t="n">
-        <v>341.0715773024029</v>
+        <v>341.0449054620968</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36995,28 +37080,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3280289994542201</v>
+        <v>-0.3284599276052131</v>
       </c>
       <c r="J21" t="n">
+        <v>408</v>
+      </c>
+      <c r="K21" t="n">
         <v>407</v>
       </c>
-      <c r="K21" t="n">
-        <v>406</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03218718378268537</v>
+        <v>0.03242775056211689</v>
       </c>
       <c r="M21" t="n">
-        <v>9.225842270520863</v>
+        <v>9.205456743923214</v>
       </c>
       <c r="N21" t="n">
-        <v>154.2171705078271</v>
+        <v>153.8400009093561</v>
       </c>
       <c r="O21" t="n">
-        <v>12.41842061245419</v>
+        <v>12.40322542362897</v>
       </c>
       <c r="P21" t="n">
-        <v>348.0873207684767</v>
+        <v>348.0922498997211</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37073,28 +37158,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.097036420616433</v>
+        <v>-0.1012324533019448</v>
       </c>
       <c r="J22" t="n">
+        <v>408</v>
+      </c>
+      <c r="K22" t="n">
         <v>407</v>
       </c>
-      <c r="K22" t="n">
-        <v>406</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.002483550232972531</v>
+        <v>0.002713628449010352</v>
       </c>
       <c r="M22" t="n">
-        <v>9.59720313726412</v>
+        <v>9.598017238488028</v>
       </c>
       <c r="N22" t="n">
-        <v>180.2671187040706</v>
+        <v>179.9894011634576</v>
       </c>
       <c r="O22" t="n">
-        <v>13.42635910081622</v>
+        <v>13.41601286386748</v>
       </c>
       <c r="P22" t="n">
-        <v>337.1838848336135</v>
+        <v>337.2318807599989</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37132,7 +37217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W408"/>
+  <dimension ref="A1:W409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84507,6 +84592,123 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-37.68548495126624,174.8118282798236</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-37.68479581291182,174.81158648170634</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-37.68410175641939,174.81136016023817</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-37.68341521333323,174.81111014660607</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-37.68266690823253,174.81105470857077</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-37.68202306196573,174.8106701308793</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-37.681448954751176,174.81006788643379</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-37.68066373978583,174.8101406662997</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-37.6799921736838,174.80985001477586</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-37.67935736839742,174.8094347924092</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-37.67870257593298,174.8090841177661</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>-37.678111872159484,174.8085263900533</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>-37.677428944032904,174.80826656746578</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>-37.67677454517546,174.80793907259647</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>-37.67614555131111,174.8075377206918</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>-37.67549488653894,174.8071785429318</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>-37.67483025089392,174.80685519587686</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>-37.67418133561381,174.80646938461584</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>-37.67349594085321,174.80622083251606</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>-37.672783747028056,174.80602971485686</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>-37.67208499626882,174.8057609551298</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W409"/>
+  <dimension ref="A1:W410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30961,6 +30961,81 @@
         <v>326.41</v>
       </c>
       <c r="W409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="C410" t="n">
+        <v>327.77</v>
+      </c>
+      <c r="D410" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="E410" t="n">
+        <v>314.69</v>
+      </c>
+      <c r="F410" t="n">
+        <v>303.81</v>
+      </c>
+      <c r="G410" t="n">
+        <v>305.71</v>
+      </c>
+      <c r="H410" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="I410" t="n">
+        <v>296.76</v>
+      </c>
+      <c r="J410" t="n">
+        <v>291.18</v>
+      </c>
+      <c r="K410" t="n">
+        <v>296.36</v>
+      </c>
+      <c r="L410" t="n">
+        <v>294.79</v>
+      </c>
+      <c r="M410" t="n">
+        <v>309.97</v>
+      </c>
+      <c r="N410" t="n">
+        <v>307.41</v>
+      </c>
+      <c r="O410" t="n">
+        <v>306.44</v>
+      </c>
+      <c r="P410" t="n">
+        <v>320.92</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>331.38</v>
+      </c>
+      <c r="R410" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="S410" t="n">
+        <v>344.84</v>
+      </c>
+      <c r="T410" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="U410" t="n">
+        <v>336.36</v>
+      </c>
+      <c r="V410" t="n">
+        <v>327.27</v>
+      </c>
+      <c r="W410" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30977,7 +31052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35430,6 +35505,16 @@
       </c>
       <c r="B445" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -35598,28 +35683,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3591974606693145</v>
+        <v>-0.3549042283553597</v>
       </c>
       <c r="J2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02392662949472057</v>
+        <v>0.0234722964557319</v>
       </c>
       <c r="M2" t="n">
-        <v>11.75352347755119</v>
+        <v>11.74007811031575</v>
       </c>
       <c r="N2" t="n">
-        <v>249.063382240696</v>
+        <v>248.6224601456216</v>
       </c>
       <c r="O2" t="n">
-        <v>15.78174205342034</v>
+        <v>15.76776649198045</v>
       </c>
       <c r="P2" t="n">
-        <v>333.2568584516781</v>
+        <v>333.207375909267</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35676,28 +35761,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3712155316783862</v>
+        <v>-0.369852881643813</v>
       </c>
       <c r="J3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008566693976200246</v>
+        <v>0.00854736970884562</v>
       </c>
       <c r="M3" t="n">
-        <v>18.38762600886922</v>
+        <v>18.34653318351307</v>
       </c>
       <c r="N3" t="n">
-        <v>754.6489203593459</v>
+        <v>752.8119753108964</v>
       </c>
       <c r="O3" t="n">
-        <v>27.47087403704778</v>
+        <v>27.4374192538383</v>
       </c>
       <c r="P3" t="n">
-        <v>334.845967968608</v>
+        <v>334.8302624620814</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35754,28 +35839,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.023959025977997</v>
+        <v>-1.026359109918196</v>
       </c>
       <c r="J4" t="n">
+        <v>409</v>
+      </c>
+      <c r="K4" t="n">
         <v>408</v>
       </c>
-      <c r="K4" t="n">
-        <v>407</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03693270379064673</v>
+        <v>0.03728088813593178</v>
       </c>
       <c r="M4" t="n">
-        <v>23.35428457714519</v>
+        <v>23.31689681024607</v>
       </c>
       <c r="N4" t="n">
-        <v>1294.518751612112</v>
+        <v>1291.399353516731</v>
       </c>
       <c r="O4" t="n">
-        <v>35.97942122397346</v>
+        <v>35.93604532383511</v>
       </c>
       <c r="P4" t="n">
-        <v>351.8029986772949</v>
+        <v>351.8306311004118</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35832,28 +35917,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.298676970490285</v>
+        <v>-2.284858263497766</v>
       </c>
       <c r="J5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K5" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1016830374048084</v>
+        <v>0.1009830465714356</v>
       </c>
       <c r="M5" t="n">
-        <v>35.18025139566122</v>
+        <v>35.12270285247692</v>
       </c>
       <c r="N5" t="n">
-        <v>2277.323255657352</v>
+        <v>2273.361181789003</v>
       </c>
       <c r="O5" t="n">
-        <v>47.72130819306353</v>
+        <v>47.67977749307354</v>
       </c>
       <c r="P5" t="n">
-        <v>348.1664383725914</v>
+        <v>348.0096794937921</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35910,28 +35995,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8824937698577415</v>
+        <v>-0.8795983620748611</v>
       </c>
       <c r="J6" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K6" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02025725304792236</v>
+        <v>0.02022659823006856</v>
       </c>
       <c r="M6" t="n">
-        <v>32.28004286243486</v>
+        <v>32.20904788524521</v>
       </c>
       <c r="N6" t="n">
-        <v>1813.683613779166</v>
+        <v>1809.217647070958</v>
       </c>
       <c r="O6" t="n">
-        <v>42.58736448501088</v>
+        <v>42.53489916610781</v>
       </c>
       <c r="P6" t="n">
-        <v>321.2871612181829</v>
+        <v>321.253972383025</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35988,28 +36073,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.009310419713682</v>
+        <v>-1.006206588093459</v>
       </c>
       <c r="J7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K7" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06365500588079509</v>
+        <v>0.06359276151674342</v>
       </c>
       <c r="M7" t="n">
-        <v>20.05284858299877</v>
+        <v>20.01137921224203</v>
       </c>
       <c r="N7" t="n">
-        <v>712.6862357162308</v>
+        <v>710.9602620988103</v>
       </c>
       <c r="O7" t="n">
-        <v>26.69618391673669</v>
+        <v>26.66383809767098</v>
       </c>
       <c r="P7" t="n">
-        <v>326.2893093557642</v>
+        <v>326.2535855859041</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36066,28 +36151,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1869928616245634</v>
+        <v>-0.1802710070544788</v>
       </c>
       <c r="J8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K8" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004708721737944455</v>
+        <v>0.004394585311137011</v>
       </c>
       <c r="M8" t="n">
-        <v>15.13105048675819</v>
+        <v>15.1183924993638</v>
       </c>
       <c r="N8" t="n">
-        <v>355.8519363288679</v>
+        <v>355.4025704799864</v>
       </c>
       <c r="O8" t="n">
-        <v>18.86403817661711</v>
+        <v>18.85212376577202</v>
       </c>
       <c r="P8" t="n">
-        <v>310.863825818031</v>
+        <v>310.7870160869252</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36144,28 +36229,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8372010569813176</v>
+        <v>-0.8294164578914847</v>
       </c>
       <c r="J9" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K9" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03642395476126026</v>
+        <v>0.03592808502800215</v>
       </c>
       <c r="M9" t="n">
-        <v>25.02001129874239</v>
+        <v>24.99548117268609</v>
       </c>
       <c r="N9" t="n">
-        <v>904.9387446935403</v>
+        <v>903.2445438700314</v>
       </c>
       <c r="O9" t="n">
-        <v>30.08219979811218</v>
+        <v>30.05402708240663</v>
       </c>
       <c r="P9" t="n">
-        <v>303.4644225132357</v>
+        <v>303.3760453026435</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36222,28 +36307,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7407004658331686</v>
+        <v>-0.7324256600479775</v>
       </c>
       <c r="J10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02304742202900156</v>
+        <v>0.02264654158979207</v>
       </c>
       <c r="M10" t="n">
-        <v>28.02429470004603</v>
+        <v>27.99549646841659</v>
       </c>
       <c r="N10" t="n">
-        <v>1120.753120457462</v>
+        <v>1118.627125539182</v>
       </c>
       <c r="O10" t="n">
-        <v>33.47765105943758</v>
+        <v>33.44588353653079</v>
       </c>
       <c r="P10" t="n">
-        <v>294.355003545422</v>
+        <v>294.2605510040821</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36300,28 +36385,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3452406868590651</v>
+        <v>-0.3405161223565453</v>
       </c>
       <c r="J11" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K11" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01595394507973447</v>
+        <v>0.01559681332553131</v>
       </c>
       <c r="M11" t="n">
-        <v>15.59927747685287</v>
+        <v>15.58384476949611</v>
       </c>
       <c r="N11" t="n">
-        <v>354.0300509784029</v>
+        <v>353.3560208256308</v>
       </c>
       <c r="O11" t="n">
-        <v>18.8156863010203</v>
+        <v>18.79776637863209</v>
       </c>
       <c r="P11" t="n">
-        <v>296.2251856179894</v>
+        <v>296.1712737924927</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36378,28 +36463,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3870593468908933</v>
+        <v>-0.3831738415809023</v>
       </c>
       <c r="J12" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K12" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01539331519084108</v>
+        <v>0.01516220244377497</v>
       </c>
       <c r="M12" t="n">
-        <v>18.02884438113055</v>
+        <v>18.00186433344997</v>
       </c>
       <c r="N12" t="n">
-        <v>465.9668985761314</v>
+        <v>464.9510483837004</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5862664343821</v>
+        <v>21.5627235845498</v>
       </c>
       <c r="P12" t="n">
-        <v>297.3246944284198</v>
+        <v>297.2806168245165</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36456,28 +36541,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4469228097285989</v>
+        <v>0.4458987738294802</v>
       </c>
       <c r="J13" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K13" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04602781542682799</v>
+        <v>0.04604703572581414</v>
       </c>
       <c r="M13" t="n">
-        <v>11.45632982652871</v>
+        <v>11.43304870286417</v>
       </c>
       <c r="N13" t="n">
-        <v>198.2106062451651</v>
+        <v>197.7358768536662</v>
       </c>
       <c r="O13" t="n">
-        <v>14.07872885757678</v>
+        <v>14.06185894018519</v>
       </c>
       <c r="P13" t="n">
-        <v>300.274349287634</v>
+        <v>300.2860632272985</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36534,28 +36619,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3456620936753719</v>
+        <v>0.343892948067112</v>
       </c>
       <c r="J14" t="n">
+        <v>409</v>
+      </c>
+      <c r="K14" t="n">
         <v>408</v>
       </c>
-      <c r="K14" t="n">
-        <v>407</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02453366727271344</v>
+        <v>0.02440690021590908</v>
       </c>
       <c r="M14" t="n">
-        <v>11.93675086262677</v>
+        <v>11.91645180775572</v>
       </c>
       <c r="N14" t="n">
-        <v>227.9615332190341</v>
+        <v>227.4323588267645</v>
       </c>
       <c r="O14" t="n">
-        <v>15.09839505441006</v>
+        <v>15.08086067924389</v>
       </c>
       <c r="P14" t="n">
-        <v>301.8356763377291</v>
+        <v>301.855889899657</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36612,28 +36697,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08510101620080369</v>
+        <v>-0.07775221997125245</v>
       </c>
       <c r="J15" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K15" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001033206563280875</v>
+        <v>0.0008657065167784195</v>
       </c>
       <c r="M15" t="n">
-        <v>14.32182179576306</v>
+        <v>14.31967467711896</v>
       </c>
       <c r="N15" t="n">
-        <v>337.488081248325</v>
+        <v>337.1676600490003</v>
       </c>
       <c r="O15" t="n">
-        <v>18.37084868067681</v>
+        <v>18.36212569527287</v>
       </c>
       <c r="P15" t="n">
-        <v>294.2169749941061</v>
+        <v>294.1332086070673</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36690,28 +36775,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01200113409874985</v>
+        <v>-0.009096805534749492</v>
       </c>
       <c r="J16" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K16" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L16" t="n">
-        <v>3.930799647156036e-05</v>
+        <v>2.268939480909449e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>9.871422269660711</v>
+        <v>9.859972204199689</v>
       </c>
       <c r="N16" t="n">
-        <v>175.0805881371561</v>
+        <v>174.7289503210054</v>
       </c>
       <c r="O16" t="n">
-        <v>13.23180215001555</v>
+        <v>13.21850787044458</v>
       </c>
       <c r="P16" t="n">
-        <v>315.5260129490749</v>
+        <v>315.4926765919175</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36768,28 +36853,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001661893880165067</v>
+        <v>0.001830606404894225</v>
       </c>
       <c r="J17" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K17" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L17" t="n">
-        <v>1.053928960992323e-06</v>
+        <v>1.284102805865217e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>8.427957927888702</v>
+        <v>8.425956645472699</v>
       </c>
       <c r="N17" t="n">
-        <v>125.4703994595102</v>
+        <v>125.2786994696613</v>
       </c>
       <c r="O17" t="n">
-        <v>11.20135703651617</v>
+        <v>11.19279676710255</v>
       </c>
       <c r="P17" t="n">
-        <v>324.5323140533276</v>
+        <v>324.4923633663908</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36846,28 +36931,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.06328391850125234</v>
+        <v>-0.05987524387339505</v>
       </c>
       <c r="J18" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K18" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001982254551312401</v>
+        <v>0.001781805725107444</v>
       </c>
       <c r="M18" t="n">
-        <v>7.395247570028491</v>
+        <v>7.394589449088201</v>
       </c>
       <c r="N18" t="n">
-        <v>96.45842195196184</v>
+        <v>96.33112251613424</v>
       </c>
       <c r="O18" t="n">
-        <v>9.821324857266552</v>
+        <v>9.814841950644658</v>
       </c>
       <c r="P18" t="n">
-        <v>330.6583282340269</v>
+        <v>330.6192573808368</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36924,28 +37009,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1537261828604742</v>
+        <v>-0.1518490593866643</v>
       </c>
       <c r="J19" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K19" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L19" t="n">
-        <v>0.008634728660974034</v>
+        <v>0.008467271008293697</v>
       </c>
       <c r="M19" t="n">
-        <v>8.931757780554177</v>
+        <v>8.918291944340602</v>
       </c>
       <c r="N19" t="n">
-        <v>129.9053965671612</v>
+        <v>129.6210215637283</v>
       </c>
       <c r="O19" t="n">
-        <v>11.39760486098554</v>
+        <v>11.38512281724393</v>
       </c>
       <c r="P19" t="n">
-        <v>345.1720228751062</v>
+        <v>345.150550472494</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37002,28 +37087,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1366068840210496</v>
+        <v>0.1365351610151648</v>
       </c>
       <c r="J20" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K20" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006725231976722035</v>
+        <v>0.006752171307372712</v>
       </c>
       <c r="M20" t="n">
-        <v>8.539351811528791</v>
+        <v>8.518846736989934</v>
       </c>
       <c r="N20" t="n">
-        <v>131.9634935885416</v>
+        <v>131.6408929910231</v>
       </c>
       <c r="O20" t="n">
-        <v>11.48753644558056</v>
+        <v>11.47348652289369</v>
       </c>
       <c r="P20" t="n">
-        <v>341.0449054620968</v>
+        <v>341.0457259010718</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37080,28 +37165,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3284599276052131</v>
+        <v>-0.3300459558482675</v>
       </c>
       <c r="J21" t="n">
+        <v>409</v>
+      </c>
+      <c r="K21" t="n">
         <v>408</v>
       </c>
-      <c r="K21" t="n">
-        <v>407</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03242775056211689</v>
+        <v>0.03288752831962383</v>
       </c>
       <c r="M21" t="n">
-        <v>9.205456743923214</v>
+        <v>9.191243430714932</v>
       </c>
       <c r="N21" t="n">
-        <v>153.8400009093561</v>
+        <v>153.4866340977761</v>
       </c>
       <c r="O21" t="n">
-        <v>12.40322542362897</v>
+        <v>12.38897227770634</v>
       </c>
       <c r="P21" t="n">
-        <v>348.0922498997211</v>
+        <v>348.1104251551507</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37158,28 +37243,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1012324533019448</v>
+        <v>-0.1049470935673607</v>
       </c>
       <c r="J22" t="n">
+        <v>409</v>
+      </c>
+      <c r="K22" t="n">
         <v>408</v>
       </c>
-      <c r="K22" t="n">
-        <v>407</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.002713628449010352</v>
+        <v>0.002928516613344589</v>
       </c>
       <c r="M22" t="n">
-        <v>9.598017238488028</v>
+        <v>9.595992411936393</v>
       </c>
       <c r="N22" t="n">
-        <v>179.9894011634576</v>
+        <v>179.6782118589595</v>
       </c>
       <c r="O22" t="n">
-        <v>13.41601286386748</v>
+        <v>13.40441016453016</v>
       </c>
       <c r="P22" t="n">
-        <v>337.2318807599989</v>
+        <v>337.2744490660483</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37217,7 +37302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W409"/>
+  <dimension ref="A1:W410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84709,6 +84794,123 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-37.6854684760038,174.81188018982468</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-37.684790265484565,174.81160396038396</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-37.68410182325562,174.8113599496535</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-37.68341979159474,174.81109572167702</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-37.68272004274488,174.8108872967487</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-37.68206299611146,174.81054430972304</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-37.681445262092105,174.81007958186845</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-37.68070849713417,174.80999713090378</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-37.680025955072836,174.80974088669922</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-37.679377316587036,174.80937035131865</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>-37.67870659824749,174.80907112400817</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>-37.67809064897067,174.80859495019197</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>-37.677416681080054,174.8083061820117</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>-37.676755417122614,174.8080041457113</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>-37.67613751228262,174.8075680478616</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>-37.675490451382245,174.8071961588336</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>-37.67482184321123,174.80688859017178</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>-37.67416628900548,174.80652914806151</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>-37.6734822579109,174.80627125521687</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>-37.6727755761358,174.80605367593435</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>-37.67208843034423,174.80575221572107</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W410"/>
+  <dimension ref="A1:W412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31038,6 +31038,156 @@
       <c r="W410" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>336.54</v>
+      </c>
+      <c r="C411" t="n">
+        <v>330.12</v>
+      </c>
+      <c r="D411" t="n">
+        <v>324.37</v>
+      </c>
+      <c r="E411" t="n">
+        <v>316.77</v>
+      </c>
+      <c r="F411" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="G411" t="n">
+        <v>328.77</v>
+      </c>
+      <c r="H411" t="n">
+        <v>324</v>
+      </c>
+      <c r="I411" t="n">
+        <v>316.42</v>
+      </c>
+      <c r="J411" t="n">
+        <v>310.52</v>
+      </c>
+      <c r="K411" t="n">
+        <v>308</v>
+      </c>
+      <c r="L411" t="n">
+        <v>306.03</v>
+      </c>
+      <c r="M411" t="n">
+        <v>307.12</v>
+      </c>
+      <c r="N411" t="n">
+        <v>304.82</v>
+      </c>
+      <c r="O411" t="n">
+        <v>311.07</v>
+      </c>
+      <c r="P411" t="n">
+        <v>325.44</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>336.15</v>
+      </c>
+      <c r="R411" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="S411" t="n">
+        <v>340.22</v>
+      </c>
+      <c r="T411" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="U411" t="n">
+        <v>342.35</v>
+      </c>
+      <c r="V411" t="n">
+        <v>330.04</v>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>336.54</v>
+      </c>
+      <c r="C412" t="n">
+        <v>330.12</v>
+      </c>
+      <c r="D412" t="n">
+        <v>324.37</v>
+      </c>
+      <c r="E412" t="n">
+        <v>316.77</v>
+      </c>
+      <c r="F412" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="G412" t="n">
+        <v>330.14</v>
+      </c>
+      <c r="H412" t="n">
+        <v>326.63</v>
+      </c>
+      <c r="I412" t="n">
+        <v>319.34</v>
+      </c>
+      <c r="J412" t="n">
+        <v>311.59</v>
+      </c>
+      <c r="K412" t="n">
+        <v>307.1</v>
+      </c>
+      <c r="L412" t="n">
+        <v>306.33</v>
+      </c>
+      <c r="M412" t="n">
+        <v>307.06</v>
+      </c>
+      <c r="N412" t="n">
+        <v>305.61</v>
+      </c>
+      <c r="O412" t="n">
+        <v>311.07</v>
+      </c>
+      <c r="P412" t="n">
+        <v>326.23</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>336.84</v>
+      </c>
+      <c r="R412" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="S412" t="n">
+        <v>342.94</v>
+      </c>
+      <c r="T412" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="U412" t="n">
+        <v>342.67</v>
+      </c>
+      <c r="V412" t="n">
+        <v>331.46</v>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31052,7 +31202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B446"/>
+  <dimension ref="A1:B448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35515,6 +35665,26 @@
       </c>
       <c r="B446" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -35683,28 +35853,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3549042283553597</v>
+        <v>-0.3419114657845564</v>
       </c>
       <c r="J2" t="n">
+        <v>411</v>
+      </c>
+      <c r="K2" t="n">
         <v>409</v>
       </c>
-      <c r="K2" t="n">
-        <v>407</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0234722964557319</v>
+        <v>0.0219764358060166</v>
       </c>
       <c r="M2" t="n">
-        <v>11.74007811031575</v>
+        <v>11.72840407497604</v>
       </c>
       <c r="N2" t="n">
-        <v>248.6224601456216</v>
+        <v>248.1815917380036</v>
       </c>
       <c r="O2" t="n">
-        <v>15.76776649198045</v>
+        <v>15.7537802364386</v>
       </c>
       <c r="P2" t="n">
-        <v>333.207375909267</v>
+        <v>333.0567422045024</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35761,28 +35931,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.369852881643813</v>
+        <v>-0.3646934276959878</v>
       </c>
       <c r="J3" t="n">
+        <v>411</v>
+      </c>
+      <c r="K3" t="n">
         <v>409</v>
       </c>
-      <c r="K3" t="n">
-        <v>407</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00854736970884562</v>
+        <v>0.00839683272864078</v>
       </c>
       <c r="M3" t="n">
-        <v>18.34653318351307</v>
+        <v>18.27196607457655</v>
       </c>
       <c r="N3" t="n">
-        <v>752.8119753108964</v>
+        <v>749.2529354831912</v>
       </c>
       <c r="O3" t="n">
-        <v>27.4374192538383</v>
+        <v>27.37248500745212</v>
       </c>
       <c r="P3" t="n">
-        <v>334.8302624620814</v>
+        <v>334.7704454806615</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35839,28 +36009,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.026359109918196</v>
+        <v>-1.026778338752133</v>
       </c>
       <c r="J4" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K4" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03728088813593178</v>
+        <v>0.03768358568145336</v>
       </c>
       <c r="M4" t="n">
-        <v>23.31689681024607</v>
+        <v>23.20656719674698</v>
       </c>
       <c r="N4" t="n">
-        <v>1291.399353516731</v>
+        <v>1285.100651814326</v>
       </c>
       <c r="O4" t="n">
-        <v>35.93604532383511</v>
+        <v>35.84830054290337</v>
       </c>
       <c r="P4" t="n">
-        <v>351.8306311004118</v>
+        <v>351.8354860641671</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35917,28 +36087,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.284858263497766</v>
+        <v>-2.254996112486</v>
       </c>
       <c r="J5" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K5" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1009830465714356</v>
+        <v>0.09938878803568774</v>
       </c>
       <c r="M5" t="n">
-        <v>35.12270285247692</v>
+        <v>35.01396566024875</v>
       </c>
       <c r="N5" t="n">
-        <v>2273.361181789003</v>
+        <v>2266.076353262288</v>
       </c>
       <c r="O5" t="n">
-        <v>47.67977749307354</v>
+        <v>47.60332292248397</v>
       </c>
       <c r="P5" t="n">
-        <v>348.0096794937921</v>
+        <v>347.6688597261021</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35995,28 +36165,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8795983620748611</v>
+        <v>-0.8461234090410045</v>
       </c>
       <c r="J6" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K6" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02022659823006856</v>
+        <v>0.018880532164115</v>
       </c>
       <c r="M6" t="n">
-        <v>32.20904788524521</v>
+        <v>32.16341144279173</v>
       </c>
       <c r="N6" t="n">
-        <v>1809.217647070958</v>
+        <v>1805.457195616482</v>
       </c>
       <c r="O6" t="n">
-        <v>42.53489916610781</v>
+        <v>42.49067186591055</v>
       </c>
       <c r="P6" t="n">
-        <v>321.253972383025</v>
+        <v>320.8679294601088</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36073,28 +36243,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.006206588093459</v>
+        <v>-0.9749029532292471</v>
       </c>
       <c r="J7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K7" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06359276151674342</v>
+        <v>0.06017957026376575</v>
       </c>
       <c r="M7" t="n">
-        <v>20.01137921224203</v>
+        <v>20.0048938845413</v>
       </c>
       <c r="N7" t="n">
-        <v>710.9602620988103</v>
+        <v>711.7664792559148</v>
       </c>
       <c r="O7" t="n">
-        <v>26.66383809767098</v>
+        <v>26.67895198946006</v>
       </c>
       <c r="P7" t="n">
-        <v>326.2535855859041</v>
+        <v>325.8911450987222</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36151,28 +36321,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1802710070544788</v>
+        <v>-0.1607057519768874</v>
       </c>
       <c r="J8" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K8" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004394585311137011</v>
+        <v>0.003513666430488449</v>
       </c>
       <c r="M8" t="n">
-        <v>15.1183924993638</v>
+        <v>15.11525787457</v>
       </c>
       <c r="N8" t="n">
-        <v>355.4025704799864</v>
+        <v>355.4635781072141</v>
       </c>
       <c r="O8" t="n">
-        <v>18.85212376577202</v>
+        <v>18.85374175348793</v>
       </c>
       <c r="P8" t="n">
-        <v>310.7870160869252</v>
+        <v>310.5620948391992</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36229,28 +36399,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8294164578914847</v>
+        <v>-0.7923167109582739</v>
       </c>
       <c r="J9" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K9" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03592808502800215</v>
+        <v>0.0329882904406319</v>
       </c>
       <c r="M9" t="n">
-        <v>24.99548117268609</v>
+        <v>25.04985353881056</v>
       </c>
       <c r="N9" t="n">
-        <v>903.2445438700314</v>
+        <v>905.2512386243715</v>
       </c>
       <c r="O9" t="n">
-        <v>30.05402708240663</v>
+        <v>30.08739335044449</v>
       </c>
       <c r="P9" t="n">
-        <v>303.3760453026435</v>
+        <v>302.952273659859</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36307,28 +36477,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7324256600479775</v>
+        <v>-0.6956845712241932</v>
       </c>
       <c r="J10" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02264654158979207</v>
+        <v>0.02057039603922906</v>
       </c>
       <c r="M10" t="n">
-        <v>27.99549646841659</v>
+        <v>28.03495293457002</v>
       </c>
       <c r="N10" t="n">
-        <v>1118.627125539182</v>
+        <v>1119.439884326503</v>
       </c>
       <c r="O10" t="n">
-        <v>33.44588353653079</v>
+        <v>33.45803168637544</v>
       </c>
       <c r="P10" t="n">
-        <v>294.2605510040821</v>
+        <v>293.8386482538561</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36385,28 +36555,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3405161223565453</v>
+        <v>-0.3196079559129729</v>
       </c>
       <c r="J11" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K11" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01559681332553131</v>
+        <v>0.0138296307816268</v>
       </c>
       <c r="M11" t="n">
-        <v>15.58384476949611</v>
+        <v>15.60862216838333</v>
       </c>
       <c r="N11" t="n">
-        <v>353.3560208256308</v>
+        <v>353.6274722683448</v>
       </c>
       <c r="O11" t="n">
-        <v>18.79776637863209</v>
+        <v>18.8049853035929</v>
       </c>
       <c r="P11" t="n">
-        <v>296.1712737924927</v>
+        <v>295.9312649498681</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36463,28 +36633,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3831738415809023</v>
+        <v>-0.3638144974124667</v>
       </c>
       <c r="J12" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K12" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01516220244377497</v>
+        <v>0.01377845850135706</v>
       </c>
       <c r="M12" t="n">
-        <v>18.00186433344997</v>
+        <v>18.00178797222577</v>
       </c>
       <c r="N12" t="n">
-        <v>464.9510483837004</v>
+        <v>464.4095470757153</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5627235845498</v>
+        <v>21.55016350461674</v>
       </c>
       <c r="P12" t="n">
-        <v>297.2806168245165</v>
+        <v>297.0596755882004</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36541,28 +36711,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4458987738294802</v>
+        <v>0.4408830244478214</v>
       </c>
       <c r="J13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04604703572581414</v>
+        <v>0.04548223428606823</v>
       </c>
       <c r="M13" t="n">
-        <v>11.43304870286417</v>
+        <v>11.40010729492786</v>
       </c>
       <c r="N13" t="n">
-        <v>197.7358768536662</v>
+        <v>196.8910833401478</v>
       </c>
       <c r="O13" t="n">
-        <v>14.06185894018519</v>
+        <v>14.03178831582588</v>
       </c>
       <c r="P13" t="n">
-        <v>300.2860632272985</v>
+        <v>300.3437793444089</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36619,28 +36789,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.343892948067112</v>
+        <v>0.3381085018142397</v>
       </c>
       <c r="J14" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K14" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02440690021590908</v>
+        <v>0.02383445543649942</v>
       </c>
       <c r="M14" t="n">
-        <v>11.91645180775572</v>
+        <v>11.88716636750016</v>
       </c>
       <c r="N14" t="n">
-        <v>227.4323588267645</v>
+        <v>226.4800185561318</v>
       </c>
       <c r="O14" t="n">
-        <v>15.08086067924389</v>
+        <v>15.04925308964308</v>
       </c>
       <c r="P14" t="n">
-        <v>301.855889899657</v>
+        <v>301.9223721663333</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36697,28 +36867,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.07775221997125245</v>
+        <v>-0.05847303834512884</v>
       </c>
       <c r="J15" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K15" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0008657065167784195</v>
+        <v>0.0004923318953066191</v>
       </c>
       <c r="M15" t="n">
-        <v>14.31967467711896</v>
+        <v>14.33649820671842</v>
       </c>
       <c r="N15" t="n">
-        <v>337.1676600490003</v>
+        <v>337.2544800446389</v>
       </c>
       <c r="O15" t="n">
-        <v>18.36212569527287</v>
+        <v>18.36448964835775</v>
       </c>
       <c r="P15" t="n">
-        <v>294.1332086070673</v>
+        <v>293.9121373156099</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36775,28 +36945,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.009096805534749492</v>
+        <v>0.001664898052779363</v>
       </c>
       <c r="J16" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K16" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L16" t="n">
-        <v>2.268939480909449e-05</v>
+        <v>7.654884655039496e-07</v>
       </c>
       <c r="M16" t="n">
-        <v>9.859972204199689</v>
+        <v>9.858348597555514</v>
       </c>
       <c r="N16" t="n">
-        <v>174.7289503210054</v>
+        <v>174.4137253121567</v>
       </c>
       <c r="O16" t="n">
-        <v>13.21850787044458</v>
+        <v>13.20657886479904</v>
       </c>
       <c r="P16" t="n">
-        <v>315.4926765919175</v>
+        <v>315.3684116205903</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36853,28 +37023,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001830606404894225</v>
+        <v>0.01394638656398342</v>
       </c>
       <c r="J17" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K17" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L17" t="n">
-        <v>1.284102805865217e-06</v>
+        <v>7.488367597796586e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>8.425956645472699</v>
+        <v>8.448448891697527</v>
       </c>
       <c r="N17" t="n">
-        <v>125.2786994696613</v>
+        <v>125.3547480394806</v>
       </c>
       <c r="O17" t="n">
-        <v>11.19279676710255</v>
+        <v>11.19619346204238</v>
       </c>
       <c r="P17" t="n">
-        <v>324.4923633663908</v>
+        <v>324.3529459109455</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36931,28 +37101,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05987524387339505</v>
+        <v>-0.04960016009177685</v>
       </c>
       <c r="J18" t="n">
+        <v>411</v>
+      </c>
+      <c r="K18" t="n">
         <v>409</v>
       </c>
-      <c r="K18" t="n">
-        <v>407</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.001781805725107444</v>
+        <v>0.001229715465883019</v>
       </c>
       <c r="M18" t="n">
-        <v>7.394589449088201</v>
+        <v>7.410808138253328</v>
       </c>
       <c r="N18" t="n">
-        <v>96.33112251613424</v>
+        <v>96.3532046686982</v>
       </c>
       <c r="O18" t="n">
-        <v>9.814841950644658</v>
+        <v>9.815966822921633</v>
       </c>
       <c r="P18" t="n">
-        <v>330.6192573808368</v>
+        <v>330.5007801967712</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37009,28 +37179,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1518490593866643</v>
+        <v>-0.1514103133450149</v>
       </c>
       <c r="J19" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K19" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L19" t="n">
-        <v>0.008467271008293697</v>
+        <v>0.008504493645882238</v>
       </c>
       <c r="M19" t="n">
-        <v>8.918291944340602</v>
+        <v>8.881370680310468</v>
       </c>
       <c r="N19" t="n">
-        <v>129.6210215637283</v>
+        <v>129.0001676463298</v>
       </c>
       <c r="O19" t="n">
-        <v>11.38512281724393</v>
+        <v>11.3578240718163</v>
       </c>
       <c r="P19" t="n">
-        <v>345.150550472494</v>
+        <v>345.1454946296577</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37087,28 +37257,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1365351610151648</v>
+        <v>0.1372594894085167</v>
       </c>
       <c r="J20" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K20" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006752171307372712</v>
+        <v>0.006893428652532507</v>
       </c>
       <c r="M20" t="n">
-        <v>8.518846736989934</v>
+        <v>8.480539573815244</v>
       </c>
       <c r="N20" t="n">
-        <v>131.6408929910231</v>
+        <v>131.0033488455005</v>
       </c>
       <c r="O20" t="n">
-        <v>11.47348652289369</v>
+        <v>11.44566943631959</v>
       </c>
       <c r="P20" t="n">
-        <v>341.0457259010718</v>
+        <v>341.0373892347454</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37165,28 +37335,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3300459558482675</v>
+        <v>-0.3268988921766986</v>
       </c>
       <c r="J21" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K21" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03288752831962383</v>
+        <v>0.03259684139269803</v>
       </c>
       <c r="M21" t="n">
-        <v>9.191243430714932</v>
+        <v>9.159896110967635</v>
       </c>
       <c r="N21" t="n">
-        <v>153.4866340977761</v>
+        <v>152.7841896639537</v>
       </c>
       <c r="O21" t="n">
-        <v>12.38897227770634</v>
+        <v>12.36059018267145</v>
       </c>
       <c r="P21" t="n">
-        <v>348.1104251551507</v>
+        <v>348.0741457699777</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37243,28 +37413,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1049470935673607</v>
+        <v>-0.1087644434535778</v>
       </c>
       <c r="J22" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K22" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002928516613344589</v>
+        <v>0.003175918013529899</v>
       </c>
       <c r="M22" t="n">
-        <v>9.595992411936393</v>
+        <v>9.570973365188323</v>
       </c>
       <c r="N22" t="n">
-        <v>179.6782118589595</v>
+        <v>178.8721217220343</v>
       </c>
       <c r="O22" t="n">
-        <v>13.40441016453016</v>
+        <v>13.37430827078673</v>
       </c>
       <c r="P22" t="n">
-        <v>337.2744490660483</v>
+        <v>337.3184506796223</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37302,7 +37472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W410"/>
+  <dimension ref="A1:W412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84911,6 +85081,240 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-37.68548294616449,174.81183459747209</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-37.68479811876939,174.81157921647207</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-37.684115524673544,174.81131677978757</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-37.68342674252863,174.81107382105128</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-37.68281023721281,174.8106031172471</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-37.68214005694597,174.81030151134817</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-37.68146123033934,174.81002900700722</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-37.680773197528694,174.8097896375083</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-37.68008920089314,174.80953657500024</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-37.67941538156156,174.80924738494167</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-37.67874335494281,174.8089523842344</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-37.67808132906803,174.80862505748203</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-37.67740821145969,174.8083335424502</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-37.67676988818544,174.8079549155639</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-37.676150397530265,174.8075194383521</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>-37.6755034303304,174.80714460799825</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>-37.674831475312956,174.80685033262935</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>-37.67415371839854,174.80657907699677</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>-37.673483800882046,174.8062655692537</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>-37.67279685597137,174.80599127294295</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>-37.672099491257235,174.8057240666897</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-37.68548294616449,174.81183459747209</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-37.68479811876939,174.81157921647207</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-37.684115524673544,174.81131677978757</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-37.68342674252863,174.81107382105128</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-37.68281023721281,174.8106031172471</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-37.68214463513284,174.8102870866235</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-37.68146997959916,174.81000129618835</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-37.680782807119435,174.80975881953572</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-37.68009270000547,174.8095252712918</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-37.6794124383979,174.8092568926559</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-37.67874433599178,174.8089492150217</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-37.678081132859475,174.80862569131963</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-37.67741079485807,174.80832519698896</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-37.67676988818544,174.8079549155639</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-37.67615264959586,174.80751094244047</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-37.67550530778649,174.80713715095763</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>-37.67483098554535,174.80685227792839</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>-37.67416111927786,174.8065496816085</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>-37.67348583876806,174.80625805949066</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>-37.67279799278972,174.80598793922618</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>-37.67210516147005,174.805709636497</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31051,7 +31051,7 @@
         <v>336.54</v>
       </c>
       <c r="C411" t="n">
-        <v>330.12</v>
+        <v>336.49</v>
       </c>
       <c r="D411" t="n">
         <v>324.37</v>
@@ -31126,7 +31126,7 @@
         <v>336.54</v>
       </c>
       <c r="C412" t="n">
-        <v>330.12</v>
+        <v>336.49</v>
       </c>
       <c r="D412" t="n">
         <v>324.37</v>
@@ -31186,6 +31186,156 @@
         <v>331.46</v>
       </c>
       <c r="W412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>339.09</v>
+      </c>
+      <c r="C413" t="n">
+        <v>339.37</v>
+      </c>
+      <c r="D413" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="E413" t="n">
+        <v>320.7</v>
+      </c>
+      <c r="F413" t="n">
+        <v>331.8</v>
+      </c>
+      <c r="G413" t="n">
+        <v>329.29</v>
+      </c>
+      <c r="H413" t="n">
+        <v>325.92</v>
+      </c>
+      <c r="I413" t="n">
+        <v>318.11</v>
+      </c>
+      <c r="J413" t="n">
+        <v>310.39</v>
+      </c>
+      <c r="K413" t="n">
+        <v>306.22</v>
+      </c>
+      <c r="L413" t="n">
+        <v>306.03</v>
+      </c>
+      <c r="M413" t="n">
+        <v>308.75</v>
+      </c>
+      <c r="N413" t="n">
+        <v>308.78</v>
+      </c>
+      <c r="O413" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="P413" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>336.61</v>
+      </c>
+      <c r="R413" t="n">
+        <v>338.49</v>
+      </c>
+      <c r="S413" t="n">
+        <v>344.34</v>
+      </c>
+      <c r="T413" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="U413" t="n">
+        <v>343.48</v>
+      </c>
+      <c r="V413" t="n">
+        <v>332.99</v>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>339.19</v>
+      </c>
+      <c r="C414" t="n">
+        <v>340.33</v>
+      </c>
+      <c r="D414" t="n">
+        <v>335.28</v>
+      </c>
+      <c r="E414" t="n">
+        <v>323.12</v>
+      </c>
+      <c r="F414" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="G414" t="n">
+        <v>328.99</v>
+      </c>
+      <c r="H414" t="n">
+        <v>326.06</v>
+      </c>
+      <c r="I414" t="n">
+        <v>318.11</v>
+      </c>
+      <c r="J414" t="n">
+        <v>306.03</v>
+      </c>
+      <c r="K414" t="n">
+        <v>304.14</v>
+      </c>
+      <c r="L414" t="n">
+        <v>307.95</v>
+      </c>
+      <c r="M414" t="n">
+        <v>311.06</v>
+      </c>
+      <c r="N414" t="n">
+        <v>310.86</v>
+      </c>
+      <c r="O414" t="n">
+        <v>313.18</v>
+      </c>
+      <c r="P414" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>336.24</v>
+      </c>
+      <c r="R414" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="S414" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="T414" t="n">
+        <v>348.37</v>
+      </c>
+      <c r="U414" t="n">
+        <v>343.75</v>
+      </c>
+      <c r="V414" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="W414" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31202,7 +31352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B448"/>
+  <dimension ref="A1:B450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35685,6 +35835,26 @@
       </c>
       <c r="B448" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -35853,28 +36023,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3419114657845564</v>
+        <v>-0.3265388810165841</v>
       </c>
       <c r="J2" t="n">
+        <v>413</v>
+      </c>
+      <c r="K2" t="n">
         <v>411</v>
       </c>
-      <c r="K2" t="n">
-        <v>409</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0219764358060166</v>
+        <v>0.02019918565816992</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72840407497604</v>
+        <v>11.72471178332755</v>
       </c>
       <c r="N2" t="n">
-        <v>248.1815917380036</v>
+        <v>248.0698150989247</v>
       </c>
       <c r="O2" t="n">
-        <v>15.7537802364386</v>
+        <v>15.75023222365069</v>
       </c>
       <c r="P2" t="n">
-        <v>333.0567422045024</v>
+        <v>332.8779583650731</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35931,28 +36101,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3646934276959878</v>
+        <v>-0.3432980083596577</v>
       </c>
       <c r="J3" t="n">
+        <v>413</v>
+      </c>
+      <c r="K3" t="n">
         <v>411</v>
       </c>
-      <c r="K3" t="n">
-        <v>409</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00839683272864078</v>
+        <v>0.007508792286911148</v>
       </c>
       <c r="M3" t="n">
-        <v>18.27196607457655</v>
+        <v>18.24632953625458</v>
       </c>
       <c r="N3" t="n">
-        <v>749.2529354831912</v>
+        <v>747.1354316722274</v>
       </c>
       <c r="O3" t="n">
-        <v>27.37248500745212</v>
+        <v>27.33377821802591</v>
       </c>
       <c r="P3" t="n">
-        <v>334.7704454806615</v>
+        <v>334.5218486166418</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36009,28 +36179,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.026778338752133</v>
+        <v>-1.017920235102187</v>
       </c>
       <c r="J4" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K4" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03768358568145336</v>
+        <v>0.03741865709522096</v>
       </c>
       <c r="M4" t="n">
-        <v>23.20656719674698</v>
+        <v>23.10629058063596</v>
       </c>
       <c r="N4" t="n">
-        <v>1285.100651814326</v>
+        <v>1279.24311767412</v>
       </c>
       <c r="O4" t="n">
-        <v>35.84830054290337</v>
+        <v>35.76650832376736</v>
       </c>
       <c r="P4" t="n">
-        <v>351.8354860641671</v>
+        <v>351.7325608057547</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36087,28 +36257,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.254996112486</v>
+        <v>-2.22038589783024</v>
       </c>
       <c r="J5" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K5" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09938878803568774</v>
+        <v>0.09734606467874174</v>
       </c>
       <c r="M5" t="n">
-        <v>35.01396566024875</v>
+        <v>34.91869185290739</v>
       </c>
       <c r="N5" t="n">
-        <v>2266.076353262288</v>
+        <v>2260.383696892817</v>
       </c>
       <c r="O5" t="n">
-        <v>47.60332292248397</v>
+        <v>47.54349268714717</v>
       </c>
       <c r="P5" t="n">
-        <v>347.6688597261021</v>
+        <v>347.2725558811668</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36165,28 +36335,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8461234090410045</v>
+        <v>-0.8121146919412503</v>
       </c>
       <c r="J6" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K6" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L6" t="n">
-        <v>0.018880532164115</v>
+        <v>0.01754249933861307</v>
       </c>
       <c r="M6" t="n">
-        <v>32.16341144279173</v>
+        <v>32.12085069298203</v>
       </c>
       <c r="N6" t="n">
-        <v>1805.457195616482</v>
+        <v>1801.984927222351</v>
       </c>
       <c r="O6" t="n">
-        <v>42.49067186591055</v>
+        <v>42.44979301742649</v>
       </c>
       <c r="P6" t="n">
-        <v>320.8679294601088</v>
+        <v>320.4744606287641</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36243,28 +36413,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9749029532292471</v>
+        <v>-0.9445810738819391</v>
       </c>
       <c r="J7" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K7" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06017957026376575</v>
+        <v>0.05695387443430144</v>
       </c>
       <c r="M7" t="n">
-        <v>20.0048938845413</v>
+        <v>19.99814061979756</v>
       </c>
       <c r="N7" t="n">
-        <v>711.7664792559148</v>
+        <v>712.3582424123734</v>
       </c>
       <c r="O7" t="n">
-        <v>26.67895198946006</v>
+        <v>26.6900401350836</v>
       </c>
       <c r="P7" t="n">
-        <v>325.8911450987222</v>
+        <v>325.5389649101664</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36321,28 +36491,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1607057519768874</v>
+        <v>-0.140889037353005</v>
       </c>
       <c r="J8" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K8" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003513666430488449</v>
+        <v>0.002716164704406498</v>
       </c>
       <c r="M8" t="n">
-        <v>15.11525787457</v>
+        <v>15.11252381274624</v>
       </c>
       <c r="N8" t="n">
-        <v>355.4635781072141</v>
+        <v>355.5899793609701</v>
       </c>
       <c r="O8" t="n">
-        <v>18.85374175348793</v>
+        <v>18.85709360853284</v>
       </c>
       <c r="P8" t="n">
-        <v>310.5620948391992</v>
+        <v>310.3335607427421</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36399,28 +36569,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7923167109582739</v>
+        <v>-0.755768374926101</v>
       </c>
       <c r="J9" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K9" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0329882904406319</v>
+        <v>0.03019889407091547</v>
       </c>
       <c r="M9" t="n">
-        <v>25.04985353881056</v>
+        <v>25.09991859793066</v>
       </c>
       <c r="N9" t="n">
-        <v>905.2512386243715</v>
+        <v>907.1342315152696</v>
       </c>
       <c r="O9" t="n">
-        <v>30.08739335044449</v>
+        <v>30.11866915245874</v>
       </c>
       <c r="P9" t="n">
-        <v>302.952273659859</v>
+        <v>302.5334502873075</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36477,28 +36647,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6956845712241932</v>
+        <v>-0.6625943532792967</v>
       </c>
       <c r="J10" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K10" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02057039603922906</v>
+        <v>0.01879892599568977</v>
       </c>
       <c r="M10" t="n">
-        <v>28.03495293457002</v>
+        <v>28.05771574183435</v>
       </c>
       <c r="N10" t="n">
-        <v>1119.439884326503</v>
+        <v>1119.157980830384</v>
       </c>
       <c r="O10" t="n">
-        <v>33.45803168637544</v>
+        <v>33.45381862852705</v>
       </c>
       <c r="P10" t="n">
-        <v>293.8386482538561</v>
+        <v>293.4574806884106</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36555,28 +36725,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3196079559129729</v>
+        <v>-0.301569729165479</v>
       </c>
       <c r="J11" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K11" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0138296307816268</v>
+        <v>0.01240517028059462</v>
       </c>
       <c r="M11" t="n">
-        <v>15.60862216838333</v>
+        <v>15.61915675663511</v>
       </c>
       <c r="N11" t="n">
-        <v>353.6274722683448</v>
+        <v>353.409345551072</v>
       </c>
       <c r="O11" t="n">
-        <v>18.8049853035929</v>
+        <v>18.7991847044246</v>
       </c>
       <c r="P11" t="n">
-        <v>295.9312649498681</v>
+        <v>295.7235501020885</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36633,28 +36803,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3638144974124667</v>
+        <v>-0.3440498367440727</v>
       </c>
       <c r="J12" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K12" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01377845850135706</v>
+        <v>0.01241726597404003</v>
       </c>
       <c r="M12" t="n">
-        <v>18.00178797222577</v>
+        <v>18.00533352349178</v>
       </c>
       <c r="N12" t="n">
-        <v>464.4095470757153</v>
+        <v>463.9800618813332</v>
       </c>
       <c r="O12" t="n">
-        <v>21.55016350461674</v>
+        <v>21.5401964216052</v>
       </c>
       <c r="P12" t="n">
-        <v>297.0596755882004</v>
+        <v>296.8333749379146</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36711,28 +36881,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4408830244478214</v>
+        <v>0.438777915525343</v>
       </c>
       <c r="J13" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K13" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04548223428606823</v>
+        <v>0.04550510706966726</v>
       </c>
       <c r="M13" t="n">
-        <v>11.40010729492786</v>
+        <v>11.35431212784102</v>
       </c>
       <c r="N13" t="n">
-        <v>196.8910833401478</v>
+        <v>195.9649502642794</v>
       </c>
       <c r="O13" t="n">
-        <v>14.03178831582588</v>
+        <v>13.99874816775698</v>
       </c>
       <c r="P13" t="n">
-        <v>300.3437793444089</v>
+        <v>300.3680671479961</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36789,28 +36959,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3381085018142397</v>
+        <v>0.3370668527232944</v>
       </c>
       <c r="J14" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K14" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02383445543649942</v>
+        <v>0.02392849333809466</v>
       </c>
       <c r="M14" t="n">
-        <v>11.88716636750016</v>
+        <v>11.83466264880182</v>
       </c>
       <c r="N14" t="n">
-        <v>226.4800185561318</v>
+        <v>225.3909241831645</v>
       </c>
       <c r="O14" t="n">
-        <v>15.04925308964308</v>
+        <v>15.01302515095357</v>
       </c>
       <c r="P14" t="n">
-        <v>301.9223721663333</v>
+        <v>301.9343715211488</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36867,28 +37037,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.05847303834512884</v>
+        <v>-0.03773428485415924</v>
       </c>
       <c r="J15" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K15" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0004923318953066191</v>
+        <v>0.000205959687640811</v>
       </c>
       <c r="M15" t="n">
-        <v>14.33649820671842</v>
+        <v>14.36066226647677</v>
       </c>
       <c r="N15" t="n">
-        <v>337.2544800446389</v>
+        <v>337.6434282989671</v>
       </c>
       <c r="O15" t="n">
-        <v>18.36448964835775</v>
+        <v>18.37507628008567</v>
       </c>
       <c r="P15" t="n">
-        <v>293.9121373156099</v>
+        <v>293.6735702951274</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36945,28 +37115,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001664898052779363</v>
+        <v>0.01270391787275923</v>
       </c>
       <c r="J16" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K16" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L16" t="n">
-        <v>7.654884655039496e-07</v>
+        <v>4.487678274445184e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>9.858348597555514</v>
+        <v>9.857725669120148</v>
       </c>
       <c r="N16" t="n">
-        <v>174.4137253121567</v>
+        <v>174.1375008285565</v>
       </c>
       <c r="O16" t="n">
-        <v>13.20657886479904</v>
+        <v>13.19611688446857</v>
       </c>
       <c r="P16" t="n">
-        <v>315.3684116205903</v>
+        <v>315.240541594568</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37023,28 +37193,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01394638656398342</v>
+        <v>0.02571390805844051</v>
       </c>
       <c r="J17" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K17" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L17" t="n">
-        <v>7.488367597796586e-05</v>
+        <v>0.0002557996472219992</v>
       </c>
       <c r="M17" t="n">
-        <v>8.448448891697527</v>
+        <v>8.469283199510485</v>
       </c>
       <c r="N17" t="n">
-        <v>125.3547480394806</v>
+        <v>125.4008665411679</v>
       </c>
       <c r="O17" t="n">
-        <v>11.19619346204238</v>
+        <v>11.1982528343116</v>
       </c>
       <c r="P17" t="n">
-        <v>324.3529459109455</v>
+        <v>324.2171119001957</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37101,28 +37271,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.04960016009177685</v>
+        <v>-0.03971235293564063</v>
       </c>
       <c r="J18" t="n">
+        <v>413</v>
+      </c>
+      <c r="K18" t="n">
         <v>411</v>
       </c>
-      <c r="K18" t="n">
-        <v>409</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.001229715465883019</v>
+        <v>0.0007929208370335283</v>
       </c>
       <c r="M18" t="n">
-        <v>7.410808138253328</v>
+        <v>7.425400992443714</v>
       </c>
       <c r="N18" t="n">
-        <v>96.3532046686982</v>
+        <v>96.34678318093712</v>
       </c>
       <c r="O18" t="n">
-        <v>9.815966822921633</v>
+        <v>9.815639723468722</v>
       </c>
       <c r="P18" t="n">
-        <v>330.5007801967712</v>
+        <v>330.386400904369</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37179,28 +37349,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1514103133450149</v>
+        <v>-0.1470542375537488</v>
       </c>
       <c r="J19" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K19" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L19" t="n">
-        <v>0.008504493645882238</v>
+        <v>0.008102000148439759</v>
       </c>
       <c r="M19" t="n">
-        <v>8.881370680310468</v>
+        <v>8.857573677554894</v>
       </c>
       <c r="N19" t="n">
-        <v>129.0001676463298</v>
+        <v>128.4710480731216</v>
       </c>
       <c r="O19" t="n">
-        <v>11.3578240718163</v>
+        <v>11.33450696206595</v>
       </c>
       <c r="P19" t="n">
-        <v>345.1454946296577</v>
+        <v>345.0951992527625</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37257,28 +37427,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1372594894085167</v>
+        <v>0.1403205850256295</v>
       </c>
       <c r="J20" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K20" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006893428652532507</v>
+        <v>0.007273102313608004</v>
       </c>
       <c r="M20" t="n">
-        <v>8.480539573815244</v>
+        <v>8.452616103470607</v>
       </c>
       <c r="N20" t="n">
-        <v>131.0033488455005</v>
+        <v>130.4152197200333</v>
       </c>
       <c r="O20" t="n">
-        <v>11.44566943631959</v>
+        <v>11.41994832387753</v>
       </c>
       <c r="P20" t="n">
-        <v>341.0373892347454</v>
+        <v>341.00204713225</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37335,28 +37505,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3268988921766986</v>
+        <v>-0.3226835746548919</v>
       </c>
       <c r="J21" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K21" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03259684139269803</v>
+        <v>0.03208763613009991</v>
       </c>
       <c r="M21" t="n">
-        <v>9.159896110967635</v>
+        <v>9.13324345289311</v>
       </c>
       <c r="N21" t="n">
-        <v>152.7841896639537</v>
+        <v>152.1262413916363</v>
       </c>
       <c r="O21" t="n">
-        <v>12.36059018267145</v>
+        <v>12.33394670783186</v>
       </c>
       <c r="P21" t="n">
-        <v>348.0741457699777</v>
+        <v>348.0253976087819</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37413,28 +37583,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1087644434535778</v>
+        <v>-0.1101704979223838</v>
       </c>
       <c r="J22" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K22" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003175918013529899</v>
+        <v>0.003291537592753579</v>
       </c>
       <c r="M22" t="n">
-        <v>9.570973365188323</v>
+        <v>9.532443067997281</v>
       </c>
       <c r="N22" t="n">
-        <v>178.8721217220343</v>
+        <v>178.0131370853828</v>
       </c>
       <c r="O22" t="n">
-        <v>13.37430827078673</v>
+        <v>13.34215638813242</v>
       </c>
       <c r="P22" t="n">
-        <v>337.3184506796223</v>
+        <v>337.3347098822651</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37472,7 +37642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85094,7 +85264,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>-37.68479811876939,174.81157921647207</t>
+          <t>-37.68481940615846,174.8115121446496</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -85211,7 +85381,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>-37.68479811876939,174.81157921647207</t>
+          <t>-37.68481940615846,174.8115121446496</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -85310,6 +85480,240 @@
         </is>
       </c>
       <c r="W412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-37.6854914678446,174.81180774746366</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-37.68482903058589,174.81148182017054</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-37.68413951882679,174.81124117983646</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-37.68343987577272,174.81103244149205</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-37.68281357897351,174.81059258816703</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-37.68214179465214,174.81029603627042</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-37.6814676176323,174.81000877705645</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-37.680778759244845,174.80977180107996</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-37.68008877576726,174.8095379483479</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-37.67940956063713,174.80926618908683</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-37.67874335494281,174.8089523842344</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-37.67808665939923,174.80860783822587</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-37.677421161146995,174.80829170949917</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-37.67677498274489,174.80793758399543</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-37.67615296317458,174.8075097594654</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-37.67550468196786,174.80713963663788</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>-37.674829407405134,174.80685854611392</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>-37.67416492855118,174.8065345516268</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>-37.67348971075019,174.80624379093967</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>-37.67280087036079,174.80597950075514</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>-37.67211127092276,174.80569408846998</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-37.68549180202803,174.81180669452203</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-37.68483223872666,174.81147171200905</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-37.6841519837373,174.81120190574725</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-37.68344796290325,174.8110069609417</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-37.68281494909513,174.81058827124392</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-37.68214079212937,174.81029919496916</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-37.68146808337229,174.81000730195575</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-37.680778759244845,174.80977180107996</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-37.68007451769061,174.80958400830676</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-37.679402758654334,174.809288162466</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-37.678749633654874,174.80893210127158</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-37.67809421342265,174.808583435472</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-37.67742796299714,174.80826973662997</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-37.67677648298279,174.80793248022016</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-37.676152991681725,174.8075096519222</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-37.675503675216014,174.80714363534082</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>-37.67483218275497,174.80684752275295</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-37.67417107780267,174.80651012751014</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>-37.673493582730615,174.80622952238713</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>-37.672801829551005,174.80597668793132</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>-37.67211175009545,174.80569286901675</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31338,6 +31338,81 @@
       <c r="W414" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="C415" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="D415" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="E415" t="n">
+        <v>324.29</v>
+      </c>
+      <c r="F415" t="n">
+        <v>336.02</v>
+      </c>
+      <c r="G415" t="n">
+        <v>333.44</v>
+      </c>
+      <c r="H415" t="n">
+        <v>329.96</v>
+      </c>
+      <c r="I415" t="n">
+        <v>323.19</v>
+      </c>
+      <c r="J415" t="n">
+        <v>300.72</v>
+      </c>
+      <c r="K415" t="n">
+        <v>300.91</v>
+      </c>
+      <c r="L415" t="n">
+        <v>310.42</v>
+      </c>
+      <c r="M415" t="n">
+        <v>313.93</v>
+      </c>
+      <c r="N415" t="n">
+        <v>319.02</v>
+      </c>
+      <c r="O415" t="n">
+        <v>317.99</v>
+      </c>
+      <c r="P415" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>337.17</v>
+      </c>
+      <c r="R415" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="S415" t="n">
+        <v>347.08</v>
+      </c>
+      <c r="T415" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="U415" t="n">
+        <v>343.43</v>
+      </c>
+      <c r="V415" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31352,7 +31427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B450"/>
+  <dimension ref="A1:B451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35855,6 +35930,16 @@
       </c>
       <c r="B450" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -36023,28 +36108,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3265388810165841</v>
+        <v>-0.3187615747932366</v>
       </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02019918565816992</v>
+        <v>0.01932138145847084</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72471178332755</v>
+        <v>11.72292517266517</v>
       </c>
       <c r="N2" t="n">
-        <v>248.0698150989247</v>
+        <v>248.0303555548633</v>
       </c>
       <c r="O2" t="n">
-        <v>15.75023222365069</v>
+        <v>15.74897950836381</v>
       </c>
       <c r="P2" t="n">
-        <v>332.8779583650731</v>
+        <v>332.7871855606219</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36101,28 +36186,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3432980083596577</v>
+        <v>-0.3335837369836831</v>
       </c>
       <c r="J3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K3" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007508792286911148</v>
+        <v>0.007120907561677381</v>
       </c>
       <c r="M3" t="n">
-        <v>18.24632953625458</v>
+        <v>18.23042527076194</v>
       </c>
       <c r="N3" t="n">
-        <v>747.1354316722274</v>
+        <v>746.1998084700386</v>
       </c>
       <c r="O3" t="n">
-        <v>27.33377821802591</v>
+        <v>27.31665807652976</v>
       </c>
       <c r="P3" t="n">
-        <v>334.5218486166418</v>
+        <v>334.4084685296713</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36179,28 +36264,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.017920235102187</v>
+        <v>-1.012237819936057</v>
       </c>
       <c r="J4" t="n">
+        <v>414</v>
+      </c>
+      <c r="K4" t="n">
         <v>413</v>
       </c>
-      <c r="K4" t="n">
-        <v>412</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03741865709522096</v>
+        <v>0.0371934373372782</v>
       </c>
       <c r="M4" t="n">
-        <v>23.10629058063596</v>
+        <v>23.05828374013924</v>
       </c>
       <c r="N4" t="n">
-        <v>1279.24311767412</v>
+        <v>1276.446030510401</v>
       </c>
       <c r="O4" t="n">
-        <v>35.76650832376736</v>
+        <v>35.72738488205372</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7325608057547</v>
+        <v>351.6663127288868</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36257,28 +36342,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.22038589783024</v>
+        <v>-2.202013350026919</v>
       </c>
       <c r="J5" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K5" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09734606467874174</v>
+        <v>0.09622537454946434</v>
       </c>
       <c r="M5" t="n">
-        <v>34.91869185290739</v>
+        <v>34.8746421464734</v>
       </c>
       <c r="N5" t="n">
-        <v>2260.383696892817</v>
+        <v>2257.932821042062</v>
       </c>
       <c r="O5" t="n">
-        <v>47.54349268714717</v>
+        <v>47.51771060396389</v>
       </c>
       <c r="P5" t="n">
-        <v>347.2725558811668</v>
+        <v>347.0614123724001</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36335,28 +36420,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8121146919412503</v>
+        <v>-0.7932717468997978</v>
       </c>
       <c r="J6" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K6" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01754249933861307</v>
+        <v>0.01680496370086471</v>
       </c>
       <c r="M6" t="n">
-        <v>32.12085069298203</v>
+        <v>32.10612168833804</v>
       </c>
       <c r="N6" t="n">
-        <v>1801.984927222351</v>
+        <v>1800.903477497161</v>
       </c>
       <c r="O6" t="n">
-        <v>42.44979301742649</v>
+        <v>42.43705311985225</v>
       </c>
       <c r="P6" t="n">
-        <v>320.4744606287641</v>
+        <v>320.2556537779428</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36413,28 +36498,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9445810738819391</v>
+        <v>-0.9273504783127715</v>
       </c>
       <c r="J7" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K7" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05695387443430144</v>
+        <v>0.05508553485277468</v>
       </c>
       <c r="M7" t="n">
-        <v>19.99814061979756</v>
+        <v>20.00256891554139</v>
       </c>
       <c r="N7" t="n">
-        <v>712.3582424123734</v>
+        <v>713.2755604806422</v>
       </c>
       <c r="O7" t="n">
-        <v>26.6900401350836</v>
+        <v>26.70721925773333</v>
       </c>
       <c r="P7" t="n">
-        <v>325.5389649101664</v>
+        <v>325.3381139690799</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36491,28 +36576,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.140889037353005</v>
+        <v>-0.1291122417201598</v>
       </c>
       <c r="J8" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K8" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002716164704406498</v>
+        <v>0.002285257367701576</v>
       </c>
       <c r="M8" t="n">
-        <v>15.11252381274624</v>
+        <v>15.11771738507025</v>
       </c>
       <c r="N8" t="n">
-        <v>355.5899793609701</v>
+        <v>356.043568459519</v>
       </c>
       <c r="O8" t="n">
-        <v>18.85709360853284</v>
+        <v>18.86911679065873</v>
       </c>
       <c r="P8" t="n">
-        <v>310.3335607427421</v>
+        <v>310.1972524259938</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36569,28 +36654,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.755768374926101</v>
+        <v>-0.7351460440495368</v>
       </c>
       <c r="J9" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K9" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03019889407091547</v>
+        <v>0.02863815419716675</v>
       </c>
       <c r="M9" t="n">
-        <v>25.09991859793066</v>
+        <v>25.13567308856758</v>
       </c>
       <c r="N9" t="n">
-        <v>907.1342315152696</v>
+        <v>908.9626588882649</v>
       </c>
       <c r="O9" t="n">
-        <v>30.11866915245874</v>
+        <v>30.14900759375447</v>
       </c>
       <c r="P9" t="n">
-        <v>302.5334502873075</v>
+        <v>302.2962552724233</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36647,28 +36732,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6625943532792967</v>
+        <v>-0.6500381538853125</v>
       </c>
       <c r="J10" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01879892599568977</v>
+        <v>0.01817376911926372</v>
       </c>
       <c r="M10" t="n">
-        <v>28.05771574183435</v>
+        <v>28.04941415893015</v>
       </c>
       <c r="N10" t="n">
-        <v>1119.157980830384</v>
+        <v>1117.918141467315</v>
       </c>
       <c r="O10" t="n">
-        <v>33.45381862852705</v>
+        <v>33.43528288301619</v>
       </c>
       <c r="P10" t="n">
-        <v>293.4574806884106</v>
+        <v>293.3123107052252</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36725,28 +36810,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.301569729165479</v>
+        <v>-0.2948426153929988</v>
       </c>
       <c r="J11" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K11" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01240517028059462</v>
+        <v>0.01191132334629552</v>
       </c>
       <c r="M11" t="n">
-        <v>15.61915675663511</v>
+        <v>15.61300059139723</v>
       </c>
       <c r="N11" t="n">
-        <v>353.409345551072</v>
+        <v>352.9637496255762</v>
       </c>
       <c r="O11" t="n">
-        <v>18.7991847044246</v>
+        <v>18.78732949691297</v>
       </c>
       <c r="P11" t="n">
-        <v>295.7235501020885</v>
+        <v>295.645800636411</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36803,28 +36888,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3440498367440727</v>
+        <v>-0.3325570675599972</v>
       </c>
       <c r="J12" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K12" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01241726597404003</v>
+        <v>0.01163930200359597</v>
       </c>
       <c r="M12" t="n">
-        <v>18.00533352349178</v>
+        <v>18.01463910571855</v>
       </c>
       <c r="N12" t="n">
-        <v>463.9800618813332</v>
+        <v>464.0978620871165</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5401964216052</v>
+        <v>21.54293067544703</v>
       </c>
       <c r="P12" t="n">
-        <v>296.8333749379146</v>
+        <v>296.7013106106365</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36881,28 +36966,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.438777915525343</v>
+        <v>0.4397441444422012</v>
       </c>
       <c r="J13" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K13" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04550510706966726</v>
+        <v>0.04591888600106364</v>
       </c>
       <c r="M13" t="n">
-        <v>11.35431212784102</v>
+        <v>11.33182648009117</v>
       </c>
       <c r="N13" t="n">
-        <v>195.9649502642794</v>
+        <v>195.500435097038</v>
       </c>
       <c r="O13" t="n">
-        <v>13.99874816775698</v>
+        <v>13.98214701313922</v>
       </c>
       <c r="P13" t="n">
-        <v>300.3680671479961</v>
+        <v>300.3568735922131</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36959,28 +37044,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3370668527232944</v>
+        <v>0.3411697122971972</v>
       </c>
       <c r="J14" t="n">
+        <v>414</v>
+      </c>
+      <c r="K14" t="n">
         <v>413</v>
       </c>
-      <c r="K14" t="n">
-        <v>412</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02392849333809466</v>
+        <v>0.02460627747817112</v>
       </c>
       <c r="M14" t="n">
-        <v>11.83466264880182</v>
+        <v>11.82509619821145</v>
       </c>
       <c r="N14" t="n">
-        <v>225.3909241831645</v>
+        <v>225.0045630071573</v>
       </c>
       <c r="O14" t="n">
-        <v>15.01302515095357</v>
+        <v>15.00015209946744</v>
       </c>
       <c r="P14" t="n">
-        <v>301.9343715211488</v>
+        <v>301.8868949733593</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37037,28 +37122,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03773428485415924</v>
+        <v>-0.02496044804167307</v>
       </c>
       <c r="J15" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K15" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L15" t="n">
-        <v>0.000205959687640811</v>
+        <v>9.018001258531694e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>14.36066226647677</v>
+        <v>14.38570239290622</v>
       </c>
       <c r="N15" t="n">
-        <v>337.6434282989671</v>
+        <v>338.3698572066285</v>
       </c>
       <c r="O15" t="n">
-        <v>18.37507628008567</v>
+        <v>18.39483235059859</v>
       </c>
       <c r="P15" t="n">
-        <v>293.6735702951274</v>
+        <v>293.5260968609567</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37115,28 +37200,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01270391787275923</v>
+        <v>0.01912220452894618</v>
       </c>
       <c r="J16" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K16" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L16" t="n">
-        <v>4.487678274445184e-05</v>
+        <v>0.0001019644429869349</v>
       </c>
       <c r="M16" t="n">
-        <v>9.857725669120148</v>
+        <v>9.861726333842544</v>
       </c>
       <c r="N16" t="n">
-        <v>174.1375008285565</v>
+        <v>174.1033721044758</v>
       </c>
       <c r="O16" t="n">
-        <v>13.19611688446857</v>
+        <v>13.19482368599428</v>
       </c>
       <c r="P16" t="n">
-        <v>315.240541594568</v>
+        <v>315.1659268562329</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37193,28 +37278,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02571390805844051</v>
+        <v>0.03189279396543122</v>
       </c>
       <c r="J17" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K17" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0002557996472219992</v>
+        <v>0.0003943351012788421</v>
       </c>
       <c r="M17" t="n">
-        <v>8.469283199510485</v>
+        <v>8.481408003773176</v>
       </c>
       <c r="N17" t="n">
-        <v>125.4008665411679</v>
+        <v>125.4590655379966</v>
       </c>
       <c r="O17" t="n">
-        <v>11.1982528343116</v>
+        <v>11.20085110775054</v>
       </c>
       <c r="P17" t="n">
-        <v>324.2171119001957</v>
+        <v>324.1455308257011</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37271,28 +37356,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03971235293564063</v>
+        <v>-0.03398231752654077</v>
       </c>
       <c r="J18" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K18" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0007929208370335283</v>
+        <v>0.000581835014506038</v>
       </c>
       <c r="M18" t="n">
-        <v>7.425400992443714</v>
+        <v>7.436472016242832</v>
       </c>
       <c r="N18" t="n">
-        <v>96.34678318093712</v>
+        <v>96.42363440961299</v>
       </c>
       <c r="O18" t="n">
-        <v>9.815639723468722</v>
+        <v>9.819553676701045</v>
       </c>
       <c r="P18" t="n">
-        <v>330.386400904369</v>
+        <v>330.3198813940164</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37349,28 +37434,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1470542375537488</v>
+        <v>-0.1440925312792884</v>
       </c>
       <c r="J19" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K19" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L19" t="n">
-        <v>0.008102000148439759</v>
+        <v>0.007816146910515132</v>
       </c>
       <c r="M19" t="n">
-        <v>8.857573677554894</v>
+        <v>8.849102317801181</v>
       </c>
       <c r="N19" t="n">
-        <v>128.4710480731216</v>
+        <v>128.2436957214119</v>
       </c>
       <c r="O19" t="n">
-        <v>11.33450696206595</v>
+        <v>11.32447330878624</v>
       </c>
       <c r="P19" t="n">
-        <v>345.0951992527625</v>
+        <v>345.0608885176794</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37427,28 +37512,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1403205850256295</v>
+        <v>0.1421880760831314</v>
       </c>
       <c r="J20" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K20" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L20" t="n">
-        <v>0.007273102313608004</v>
+        <v>0.007502762857654166</v>
       </c>
       <c r="M20" t="n">
-        <v>8.452616103470607</v>
+        <v>8.440184002441416</v>
       </c>
       <c r="N20" t="n">
-        <v>130.4152197200333</v>
+        <v>130.133192664747</v>
       </c>
       <c r="O20" t="n">
-        <v>11.41994832387753</v>
+        <v>11.40759364041106</v>
       </c>
       <c r="P20" t="n">
-        <v>341.00204713225</v>
+        <v>340.980412646921</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37505,28 +37590,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3226835746548919</v>
+        <v>-0.3206822498062754</v>
       </c>
       <c r="J21" t="n">
+        <v>414</v>
+      </c>
+      <c r="K21" t="n">
         <v>413</v>
       </c>
-      <c r="K21" t="n">
-        <v>412</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03208763613009991</v>
+        <v>0.0318536258626182</v>
       </c>
       <c r="M21" t="n">
-        <v>9.13324345289311</v>
+        <v>9.119476927048991</v>
       </c>
       <c r="N21" t="n">
-        <v>152.1262413916363</v>
+        <v>151.7957124457292</v>
       </c>
       <c r="O21" t="n">
-        <v>12.33394670783186</v>
+        <v>12.32054026598384</v>
       </c>
       <c r="P21" t="n">
-        <v>348.0253976087819</v>
+        <v>348.0021706798096</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37583,28 +37668,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1101704979223838</v>
+        <v>-0.1099481017903411</v>
       </c>
       <c r="J22" t="n">
+        <v>414</v>
+      </c>
+      <c r="K22" t="n">
         <v>413</v>
       </c>
-      <c r="K22" t="n">
-        <v>412</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.003291537592753579</v>
+        <v>0.00329510467674532</v>
       </c>
       <c r="M22" t="n">
-        <v>9.532443067997281</v>
+        <v>9.510239518411472</v>
       </c>
       <c r="N22" t="n">
-        <v>178.0131370853828</v>
+        <v>177.582579510102</v>
       </c>
       <c r="O22" t="n">
-        <v>13.34215638813242</v>
+        <v>13.3260113878873</v>
       </c>
       <c r="P22" t="n">
-        <v>337.3347098822651</v>
+        <v>337.3321288024537</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37642,7 +37727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85719,6 +85804,123 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-37.68549283799654,174.8118034304029</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-37.68484620749647,174.81142769937873</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-37.68415408906945,174.81119527232065</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-37.68345187279499,174.8109946418306</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-37.68282768119353,174.8105481554384</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-37.68215566287513,174.81025234092883</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-37.681481057550165,174.80996620985664</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-37.680795477286985,174.80971818623738</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-37.680057152899195,174.8096401042411</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-37.679392195951955,174.80932228458028</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-37.678757710951324,174.80890600807982</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-37.678103598717634,174.80855311689183</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-37.67745464713988,174.8081835353337</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-37.6767915166047,174.8078813361273</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-37.67615849356076,174.80748889608498</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-37.6755062057001,174.80713358454676</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>-37.67483539345254,174.80683477023626</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>-37.67417238383775,174.80650494008657</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>-37.67349375740639,174.80622887869302</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>-37.67280069273295,174.80598002164845</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>-37.67211869809792,174.80567518694338</t>
+        </is>
+      </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31360,16 +31360,16 @@
         <v>324.29</v>
       </c>
       <c r="F415" t="n">
-        <v>336.02</v>
+        <v>330.24</v>
       </c>
       <c r="G415" t="n">
-        <v>333.44</v>
+        <v>327.28</v>
       </c>
       <c r="H415" t="n">
         <v>329.96</v>
       </c>
       <c r="I415" t="n">
-        <v>323.19</v>
+        <v>313.93</v>
       </c>
       <c r="J415" t="n">
         <v>300.72</v>
@@ -31378,13 +31378,13 @@
         <v>300.91</v>
       </c>
       <c r="L415" t="n">
-        <v>310.42</v>
+        <v>305.36</v>
       </c>
       <c r="M415" t="n">
         <v>313.93</v>
       </c>
       <c r="N415" t="n">
-        <v>319.02</v>
+        <v>315.02</v>
       </c>
       <c r="O415" t="n">
         <v>317.99</v>
@@ -31411,6 +31411,156 @@
         <v>334.85</v>
       </c>
       <c r="W415" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>337.98</v>
+      </c>
+      <c r="C416" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="D416" t="n">
+        <v>338.74</v>
+      </c>
+      <c r="E416" t="n">
+        <v>326.86</v>
+      </c>
+      <c r="F416" t="n">
+        <v>318.55</v>
+      </c>
+      <c r="G416" t="n">
+        <v>320.48</v>
+      </c>
+      <c r="H416" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="I416" t="n">
+        <v>307.12</v>
+      </c>
+      <c r="J416" t="n">
+        <v>295.42</v>
+      </c>
+      <c r="K416" t="n">
+        <v>297.8</v>
+      </c>
+      <c r="L416" t="n">
+        <v>301.82</v>
+      </c>
+      <c r="M416" t="n">
+        <v>313.93</v>
+      </c>
+      <c r="N416" t="n">
+        <v>315.22</v>
+      </c>
+      <c r="O416" t="n">
+        <v>316.94</v>
+      </c>
+      <c r="P416" t="n">
+        <v>327.53</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>336.43</v>
+      </c>
+      <c r="R416" t="n">
+        <v>339.97</v>
+      </c>
+      <c r="S416" t="n">
+        <v>348.19</v>
+      </c>
+      <c r="T416" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="U416" t="n">
+        <v>342.11</v>
+      </c>
+      <c r="V416" t="n">
+        <v>333.31</v>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="C417" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="D417" t="n">
+        <v>338.74</v>
+      </c>
+      <c r="E417" t="n">
+        <v>326.86</v>
+      </c>
+      <c r="F417" t="n">
+        <v>305.3</v>
+      </c>
+      <c r="G417" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="H417" t="n">
+        <v>321.22</v>
+      </c>
+      <c r="I417" t="n">
+        <v>299</v>
+      </c>
+      <c r="J417" t="n">
+        <v>288.74</v>
+      </c>
+      <c r="K417" t="n">
+        <v>293.94</v>
+      </c>
+      <c r="L417" t="n">
+        <v>296.96</v>
+      </c>
+      <c r="M417" t="n">
+        <v>312.79</v>
+      </c>
+      <c r="N417" t="n">
+        <v>315.23</v>
+      </c>
+      <c r="O417" t="n">
+        <v>315.31</v>
+      </c>
+      <c r="P417" t="n">
+        <v>326.92</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="R417" t="n">
+        <v>339.01</v>
+      </c>
+      <c r="S417" t="n">
+        <v>349.66</v>
+      </c>
+      <c r="T417" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="U417" t="n">
+        <v>341.13</v>
+      </c>
+      <c r="V417" t="n">
+        <v>331.92</v>
+      </c>
+      <c r="W417" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -31427,7 +31577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B451"/>
+  <dimension ref="A1:B453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35940,6 +36090,26 @@
       </c>
       <c r="B451" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>
@@ -36108,28 +36278,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3187615747932366</v>
+        <v>-0.3059276879371445</v>
       </c>
       <c r="J2" t="n">
+        <v>416</v>
+      </c>
+      <c r="K2" t="n">
         <v>414</v>
       </c>
-      <c r="K2" t="n">
-        <v>412</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01932138145847084</v>
+        <v>0.0179498414001642</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72292517266517</v>
+        <v>11.70999845066213</v>
       </c>
       <c r="N2" t="n">
-        <v>248.0303555548633</v>
+        <v>247.6065156398278</v>
       </c>
       <c r="O2" t="n">
-        <v>15.74897950836381</v>
+        <v>15.73551764766027</v>
       </c>
       <c r="P2" t="n">
-        <v>332.7871855606219</v>
+        <v>332.6370084537134</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36186,28 +36356,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3335837369836831</v>
+        <v>-0.3152749470231219</v>
       </c>
       <c r="J3" t="n">
+        <v>416</v>
+      </c>
+      <c r="K3" t="n">
         <v>414</v>
       </c>
-      <c r="K3" t="n">
-        <v>412</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.007120907561677381</v>
+        <v>0.006417486665180161</v>
       </c>
       <c r="M3" t="n">
-        <v>18.23042527076194</v>
+        <v>18.19566571630709</v>
       </c>
       <c r="N3" t="n">
-        <v>746.1998084700386</v>
+        <v>744.1651582686878</v>
       </c>
       <c r="O3" t="n">
-        <v>27.31665807652976</v>
+        <v>27.27939072392725</v>
       </c>
       <c r="P3" t="n">
-        <v>334.4084685296713</v>
+        <v>334.1942206073372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36264,28 +36434,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.012237819936057</v>
+        <v>-0.9981447747620191</v>
       </c>
       <c r="J4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0371934373372782</v>
+        <v>0.0365375916179238</v>
       </c>
       <c r="M4" t="n">
-        <v>23.05828374013924</v>
+        <v>22.96699977576293</v>
       </c>
       <c r="N4" t="n">
-        <v>1276.446030510401</v>
+        <v>1271.222767016327</v>
       </c>
       <c r="O4" t="n">
-        <v>35.72738488205372</v>
+        <v>35.65421106989085</v>
       </c>
       <c r="P4" t="n">
-        <v>351.6663127288868</v>
+        <v>351.5015757603558</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36342,28 +36512,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.202013350026919</v>
+        <v>-2.163131940341485</v>
       </c>
       <c r="J5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K5" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09622537454946434</v>
+        <v>0.09378168540611431</v>
       </c>
       <c r="M5" t="n">
-        <v>34.8746421464734</v>
+        <v>34.79273037685515</v>
       </c>
       <c r="N5" t="n">
-        <v>2257.932821042062</v>
+        <v>2253.90275459847</v>
       </c>
       <c r="O5" t="n">
-        <v>47.51771060396389</v>
+        <v>47.47528572424257</v>
       </c>
       <c r="P5" t="n">
-        <v>347.0614123724001</v>
+        <v>346.6133507547462</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36420,28 +36590,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7932717468997978</v>
+        <v>-0.7833248885218924</v>
       </c>
       <c r="J6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01680496370086471</v>
+        <v>0.01655844903014403</v>
       </c>
       <c r="M6" t="n">
-        <v>32.10612168833804</v>
+        <v>31.98178919730535</v>
       </c>
       <c r="N6" t="n">
-        <v>1800.903477497161</v>
+        <v>1792.076183395129</v>
       </c>
       <c r="O6" t="n">
-        <v>42.43705311985225</v>
+        <v>42.33292079924476</v>
       </c>
       <c r="P6" t="n">
-        <v>320.2556537779428</v>
+        <v>320.1398122888822</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36498,28 +36668,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9273504783127715</v>
+        <v>-0.9110810621500245</v>
       </c>
       <c r="J7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K7" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05508553485277468</v>
+        <v>0.05374663000664515</v>
       </c>
       <c r="M7" t="n">
-        <v>20.00256891554139</v>
+        <v>19.95412259289703</v>
       </c>
       <c r="N7" t="n">
-        <v>713.2755604806422</v>
+        <v>710.5432634136064</v>
       </c>
       <c r="O7" t="n">
-        <v>26.70721925773333</v>
+        <v>26.65601739595783</v>
       </c>
       <c r="P7" t="n">
-        <v>325.3381139690799</v>
+        <v>325.1478707215031</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36576,28 +36746,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1291122417201598</v>
+        <v>-0.1114473021224731</v>
       </c>
       <c r="J8" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K8" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002285257367701576</v>
+        <v>0.001713720683910402</v>
       </c>
       <c r="M8" t="n">
-        <v>15.11771738507025</v>
+        <v>15.10671117110463</v>
       </c>
       <c r="N8" t="n">
-        <v>356.043568459519</v>
+        <v>355.8599648960514</v>
       </c>
       <c r="O8" t="n">
-        <v>18.86911679065873</v>
+        <v>18.86425097627922</v>
       </c>
       <c r="P8" t="n">
-        <v>310.1972524259938</v>
+        <v>309.9922749838073</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36654,28 +36824,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7351460440495368</v>
+        <v>-0.7193746141240127</v>
       </c>
       <c r="J9" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K9" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02863815419716675</v>
+        <v>0.02771821060345414</v>
       </c>
       <c r="M9" t="n">
-        <v>25.13567308856758</v>
+        <v>25.08718967668495</v>
       </c>
       <c r="N9" t="n">
-        <v>908.9626588882649</v>
+        <v>904.9375455856073</v>
       </c>
       <c r="O9" t="n">
-        <v>30.14900759375447</v>
+        <v>30.08217986758286</v>
       </c>
       <c r="P9" t="n">
-        <v>302.2962552724233</v>
+        <v>302.1142514569767</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36732,28 +36902,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6500381538853125</v>
+        <v>-0.6339540259028766</v>
       </c>
       <c r="J10" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K10" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01817376911926372</v>
+        <v>0.01745651250158031</v>
       </c>
       <c r="M10" t="n">
-        <v>28.04941415893015</v>
+        <v>27.98985427244529</v>
       </c>
       <c r="N10" t="n">
-        <v>1117.918141467315</v>
+        <v>1113.767055573212</v>
       </c>
       <c r="O10" t="n">
-        <v>33.43528288301619</v>
+        <v>33.37314872128808</v>
       </c>
       <c r="P10" t="n">
-        <v>293.3123107052252</v>
+        <v>293.1258857298589</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36810,28 +36980,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2948426153929988</v>
+        <v>-0.2866930077220538</v>
       </c>
       <c r="J11" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K11" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01191132334629552</v>
+        <v>0.01137484924803811</v>
       </c>
       <c r="M11" t="n">
-        <v>15.61300059139723</v>
+        <v>15.57519493866271</v>
       </c>
       <c r="N11" t="n">
-        <v>352.9637496255762</v>
+        <v>351.5653757740549</v>
       </c>
       <c r="O11" t="n">
-        <v>18.78732949691297</v>
+        <v>18.75007668715131</v>
       </c>
       <c r="P11" t="n">
-        <v>295.645800636411</v>
+        <v>295.5513775537433</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36888,28 +37058,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3325570675599972</v>
+        <v>-0.323513321261383</v>
       </c>
       <c r="J12" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K12" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01163930200359597</v>
+        <v>0.01113064925298757</v>
       </c>
       <c r="M12" t="n">
-        <v>18.01463910571855</v>
+        <v>17.96817282594228</v>
       </c>
       <c r="N12" t="n">
-        <v>464.0978620871165</v>
+        <v>462.0067860993946</v>
       </c>
       <c r="O12" t="n">
-        <v>21.54293067544703</v>
+        <v>21.49434311858342</v>
       </c>
       <c r="P12" t="n">
-        <v>296.7013106106365</v>
+        <v>296.5970523258615</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36966,28 +37136,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4397441444422012</v>
+        <v>0.4410500015768719</v>
       </c>
       <c r="J13" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K13" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04591888600106364</v>
+        <v>0.0466304150719008</v>
       </c>
       <c r="M13" t="n">
-        <v>11.33182648009117</v>
+        <v>11.28395861430189</v>
       </c>
       <c r="N13" t="n">
-        <v>195.500435097038</v>
+        <v>194.5702444169473</v>
       </c>
       <c r="O13" t="n">
-        <v>13.98214701313922</v>
+        <v>13.94884383800132</v>
       </c>
       <c r="P13" t="n">
-        <v>300.3568735922131</v>
+        <v>300.3417111573935</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37044,28 +37214,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3411697122971972</v>
+        <v>0.3434481209667966</v>
       </c>
       <c r="J14" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K14" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02460627747817112</v>
+        <v>0.02518153038691029</v>
       </c>
       <c r="M14" t="n">
-        <v>11.82509619821145</v>
+        <v>11.77858086504592</v>
       </c>
       <c r="N14" t="n">
-        <v>225.0045630071573</v>
+        <v>223.890359798939</v>
       </c>
       <c r="O14" t="n">
-        <v>15.00015209946744</v>
+        <v>14.96296627674269</v>
       </c>
       <c r="P14" t="n">
-        <v>301.8868949733593</v>
+        <v>301.8603974120419</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37122,28 +37292,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02496044804167307</v>
+        <v>-0.001692969036524355</v>
       </c>
       <c r="J15" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K15" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L15" t="n">
-        <v>9.018001258531694e-05</v>
+        <v>4.159929506419857e-07</v>
       </c>
       <c r="M15" t="n">
-        <v>14.38570239290622</v>
+        <v>14.42446150309362</v>
       </c>
       <c r="N15" t="n">
-        <v>338.3698572066285</v>
+        <v>339.3155921264712</v>
       </c>
       <c r="O15" t="n">
-        <v>18.39483235059859</v>
+        <v>18.42052095154942</v>
       </c>
       <c r="P15" t="n">
-        <v>293.5260968609567</v>
+        <v>293.2567619936318</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37200,28 +37370,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01912220452894618</v>
+        <v>0.03069483400502446</v>
       </c>
       <c r="J16" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K16" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001019644429869349</v>
+        <v>0.0002644106592620821</v>
       </c>
       <c r="M16" t="n">
-        <v>9.861726333842544</v>
+        <v>9.863909962919209</v>
       </c>
       <c r="N16" t="n">
-        <v>174.1033721044758</v>
+        <v>173.8970851968647</v>
       </c>
       <c r="O16" t="n">
-        <v>13.19482368599428</v>
+        <v>13.18700440573464</v>
       </c>
       <c r="P16" t="n">
-        <v>315.1659268562329</v>
+        <v>315.0310336733286</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37278,28 +37448,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03189279396543122</v>
+        <v>0.04323848929668112</v>
       </c>
       <c r="J17" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K17" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0003943351012788421</v>
+        <v>0.0007284529295505937</v>
       </c>
       <c r="M17" t="n">
-        <v>8.481408003773176</v>
+        <v>8.500667557859368</v>
       </c>
       <c r="N17" t="n">
-        <v>125.4590655379966</v>
+        <v>125.4676628248652</v>
       </c>
       <c r="O17" t="n">
-        <v>11.20085110775054</v>
+        <v>11.20123487946151</v>
       </c>
       <c r="P17" t="n">
-        <v>324.1455308257011</v>
+        <v>324.0137436902314</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37356,28 +37526,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03398231752654077</v>
+        <v>-0.02390508889605967</v>
       </c>
       <c r="J18" t="n">
+        <v>416</v>
+      </c>
+      <c r="K18" t="n">
         <v>414</v>
       </c>
-      <c r="K18" t="n">
-        <v>412</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.000581835014506038</v>
+        <v>0.0002895063964494238</v>
       </c>
       <c r="M18" t="n">
-        <v>7.436472016242832</v>
+        <v>7.451739351734799</v>
       </c>
       <c r="N18" t="n">
-        <v>96.42363440961299</v>
+        <v>96.44182375809648</v>
       </c>
       <c r="O18" t="n">
-        <v>9.819553676701045</v>
+        <v>9.820479813028307</v>
       </c>
       <c r="P18" t="n">
-        <v>330.3198813940164</v>
+        <v>330.2025874493947</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37434,28 +37604,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1440925312792884</v>
+        <v>-0.136406014718027</v>
       </c>
       <c r="J19" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K19" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007816146910515132</v>
+        <v>0.007066269150455051</v>
       </c>
       <c r="M19" t="n">
-        <v>8.849102317801181</v>
+        <v>8.83976808587628</v>
       </c>
       <c r="N19" t="n">
-        <v>128.2436957214119</v>
+        <v>127.9104088910021</v>
       </c>
       <c r="O19" t="n">
-        <v>11.32447330878624</v>
+        <v>11.30974840087091</v>
       </c>
       <c r="P19" t="n">
-        <v>345.0608885176794</v>
+        <v>344.9715968225319</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37512,28 +37682,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1421880760831314</v>
+        <v>0.1445222770315993</v>
       </c>
       <c r="J20" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K20" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L20" t="n">
-        <v>0.007502762857654166</v>
+        <v>0.00782677326064285</v>
       </c>
       <c r="M20" t="n">
-        <v>8.440184002441416</v>
+        <v>8.40955370893626</v>
       </c>
       <c r="N20" t="n">
-        <v>130.133192664747</v>
+        <v>129.5337979227804</v>
       </c>
       <c r="O20" t="n">
-        <v>11.40759364041106</v>
+        <v>11.38129157533452</v>
       </c>
       <c r="P20" t="n">
-        <v>340.980412646921</v>
+        <v>340.9533020943684</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37590,28 +37760,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3206822498062754</v>
+        <v>-0.3185347127328282</v>
       </c>
       <c r="J21" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K21" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0318536258626182</v>
+        <v>0.03175047929826857</v>
       </c>
       <c r="M21" t="n">
-        <v>9.119476927048991</v>
+        <v>9.084601045996351</v>
       </c>
       <c r="N21" t="n">
-        <v>151.7957124457292</v>
+        <v>151.0871803666553</v>
       </c>
       <c r="O21" t="n">
-        <v>12.32054026598384</v>
+        <v>12.29175253438887</v>
       </c>
       <c r="P21" t="n">
-        <v>348.0021706798096</v>
+        <v>347.9771853589511</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37668,28 +37838,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1099481017903411</v>
+        <v>-0.1117465477862035</v>
       </c>
       <c r="J22" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K22" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00329510467674532</v>
+        <v>0.003437985113865727</v>
       </c>
       <c r="M22" t="n">
-        <v>9.510239518411472</v>
+        <v>9.474457116970491</v>
       </c>
       <c r="N22" t="n">
-        <v>177.582579510102</v>
+        <v>176.7443930507174</v>
       </c>
       <c r="O22" t="n">
-        <v>13.3260113878873</v>
+        <v>13.29452492760525</v>
       </c>
       <c r="P22" t="n">
-        <v>337.3321288024537</v>
+        <v>337.3530640699848</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37727,7 +37897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85832,12 +86002,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>-37.68282768119353,174.8105481554384</t>
+          <t>-37.68280836582641,174.8106090135315</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>-37.68215566287513,174.81025234092883</t>
+          <t>-37.68213507774808,174.8103171995503</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -85847,7 +86017,7 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>-37.680795477286985,174.80971818623738</t>
+          <t>-37.6807650030427,174.80981591721127</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -85862,7 +86032,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>-37.678757710951324,174.80890600807982</t>
+          <t>-37.67874116393309,174.80895946214247</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -85872,7 +86042,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>-37.67745464713988,174.8081835353337</t>
+          <t>-37.67744156668546,174.80822579087908</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -85916,6 +86086,240 @@
         </is>
       </c>
       <c r="W415" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-37.68548775840812,174.81181943511515</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-37.68484617407836,174.81142780467212</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-37.68416354635064,174.8111654745424</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-37.68346046118529,174.81096758189807</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-37.68276930056979,174.81073209839852</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-37.682112353866096,174.81038879668677</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-37.68147343938075,174.8099903382961</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-37.68074259158794,174.8098877905852</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-37.680039820783826,174.8096960945064</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-37.67938202566284,174.8093551389904</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-37.678729587546584,174.8089968588436</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-37.678103598717634,174.80855311689183</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-37.67744222070853,174.8082236781022</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-37.676788234838774,174.80789250064004</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-37.6761563555253,174.80749696182522</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-37.6755041921967,174.80714158195283</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-37.674833434383,174.80684255143305</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>-37.674175404043,174.80649294416887</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>-37.67349064235464,174.8062403579046</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>-37.67279600335755,174.80599377323048</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>-37.67211254871656,174.8056908365947</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-37.685481408919614,174.81183944100232</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-37.68484072692841,174.8114449674941</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-37.68416354635064,174.8111654745424</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-37.68346046118529,174.81096758189807</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-37.682725022004895,174.81087160845834</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-37.68210540302311,174.8104106969783</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-37.68145198206539,174.81005829828376</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-37.68071586891635,174.8099734897626</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-37.68001797574106,174.80976666333063</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-37.67936940271921,174.80939591647686</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-37.6787136945225,174.80904820005776</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-37.678099870761656,174.80856515981313</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-37.67744225340969,174.80822357246333</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-37.67678314028582,174.80790983221496</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-37.676154616589386,174.80750352196023</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-37.67550381126357,174.80714309497554</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-37.67483082228949,174.8068529263614</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>-37.67417940377244,174.80647705768172</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>-37.67348912849733,174.80624593658655</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>-37.672792521850546,174.8060039827372</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>-37.672106998299185,174.80570496192706</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W417"/>
+  <dimension ref="A1:W418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31501,13 +31501,13 @@
         <v>336.08</v>
       </c>
       <c r="C417" t="n">
-        <v>342.87</v>
+        <v>324.71</v>
       </c>
       <c r="D417" t="n">
-        <v>338.74</v>
+        <v>326.27</v>
       </c>
       <c r="E417" t="n">
-        <v>326.86</v>
+        <v>315.15</v>
       </c>
       <c r="F417" t="n">
         <v>305.3</v>
@@ -31558,11 +31558,86 @@
         <v>341.13</v>
       </c>
       <c r="V417" t="n">
-        <v>331.92</v>
+        <v>315.06</v>
       </c>
       <c r="W417" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="C418" t="n">
+        <v>322.82</v>
+      </c>
+      <c r="D418" t="n">
+        <v>331.2</v>
+      </c>
+      <c r="E418" t="n">
+        <v>316.15</v>
+      </c>
+      <c r="F418" t="n">
+        <v>295.69</v>
+      </c>
+      <c r="G418" t="n">
+        <v>313.55</v>
+      </c>
+      <c r="H418" t="n">
+        <v>310.28</v>
+      </c>
+      <c r="I418" t="n">
+        <v>292.99</v>
+      </c>
+      <c r="J418" t="n">
+        <v>275.95</v>
+      </c>
+      <c r="K418" t="n">
+        <v>285.89</v>
+      </c>
+      <c r="L418" t="n">
+        <v>288.22</v>
+      </c>
+      <c r="M418" t="n">
+        <v>319.92</v>
+      </c>
+      <c r="N418" t="n">
+        <v>321</v>
+      </c>
+      <c r="O418" t="n">
+        <v>319.48</v>
+      </c>
+      <c r="P418" t="n">
+        <v>323.19</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="R418" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="S418" t="n">
+        <v>354.72</v>
+      </c>
+      <c r="T418" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="U418" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="V418" t="n">
+        <v>287.48</v>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B453"/>
+  <dimension ref="A1:B454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36110,6 +36185,16 @@
       </c>
       <c r="B453" t="n">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -36278,28 +36363,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3059276879371445</v>
+        <v>-0.300405528219557</v>
       </c>
       <c r="J2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0179498414001642</v>
+        <v>0.01738796056046255</v>
       </c>
       <c r="M2" t="n">
-        <v>11.70999845066213</v>
+        <v>11.70049575426821</v>
       </c>
       <c r="N2" t="n">
-        <v>247.6065156398278</v>
+        <v>247.2933558483419</v>
       </c>
       <c r="O2" t="n">
-        <v>15.73551764766027</v>
+        <v>15.72556376885554</v>
       </c>
       <c r="P2" t="n">
-        <v>332.6370084537134</v>
+        <v>332.5720464516596</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36356,28 +36441,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3152749470231219</v>
+        <v>-0.325880711600689</v>
       </c>
       <c r="J3" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006417486665180161</v>
+        <v>0.006895337464726037</v>
       </c>
       <c r="M3" t="n">
-        <v>18.19566571630709</v>
+        <v>18.13888569570353</v>
       </c>
       <c r="N3" t="n">
-        <v>744.1651582686878</v>
+        <v>741.6858259788227</v>
       </c>
       <c r="O3" t="n">
-        <v>27.27939072392725</v>
+        <v>27.23390948760061</v>
       </c>
       <c r="P3" t="n">
-        <v>334.1942206073372</v>
+        <v>334.3185159776411</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36434,28 +36519,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9981447747620191</v>
+        <v>-1.001165361846247</v>
       </c>
       <c r="J4" t="n">
+        <v>417</v>
+      </c>
+      <c r="K4" t="n">
         <v>416</v>
       </c>
-      <c r="K4" t="n">
-        <v>415</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0365375916179238</v>
+        <v>0.03694566118324571</v>
       </c>
       <c r="M4" t="n">
-        <v>22.96699977576293</v>
+        <v>22.90735316993993</v>
       </c>
       <c r="N4" t="n">
-        <v>1271.222767016327</v>
+        <v>1267.81060199269</v>
       </c>
       <c r="O4" t="n">
-        <v>35.65421106989085</v>
+        <v>35.60632811724189</v>
       </c>
       <c r="P4" t="n">
-        <v>351.5015757603558</v>
+        <v>351.5367482713746</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36512,28 +36597,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.163131940341485</v>
+        <v>-2.155102176239239</v>
       </c>
       <c r="J5" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09378168540611431</v>
+        <v>0.0935968253574837</v>
       </c>
       <c r="M5" t="n">
-        <v>34.79273037685515</v>
+        <v>34.72523887625047</v>
       </c>
       <c r="N5" t="n">
-        <v>2253.90275459847</v>
+        <v>2248.303442585077</v>
       </c>
       <c r="O5" t="n">
-        <v>47.47528572424257</v>
+        <v>47.41627824476608</v>
       </c>
       <c r="P5" t="n">
-        <v>346.6133507547462</v>
+        <v>346.5200045561626</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36590,28 +36675,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7833248885218924</v>
+        <v>-0.7851073489068791</v>
       </c>
       <c r="J6" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01655844903014403</v>
+        <v>0.01671716919314359</v>
       </c>
       <c r="M6" t="n">
-        <v>31.98178919730535</v>
+        <v>31.91439314118885</v>
       </c>
       <c r="N6" t="n">
-        <v>1792.076183395129</v>
+        <v>1787.703258259037</v>
       </c>
       <c r="O6" t="n">
-        <v>42.33292079924476</v>
+        <v>42.28124002745233</v>
       </c>
       <c r="P6" t="n">
-        <v>320.1398122888822</v>
+        <v>320.1606793623088</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36668,28 +36753,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9110810621500245</v>
+        <v>-0.9044399603612946</v>
       </c>
       <c r="J7" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05374663000664515</v>
+        <v>0.05324697119824695</v>
       </c>
       <c r="M7" t="n">
-        <v>19.95412259289703</v>
+        <v>19.92574618607618</v>
       </c>
       <c r="N7" t="n">
-        <v>710.5432634136064</v>
+        <v>709.173620073968</v>
       </c>
       <c r="O7" t="n">
-        <v>26.65601739595783</v>
+        <v>26.63031393119443</v>
       </c>
       <c r="P7" t="n">
-        <v>325.1478707215031</v>
+        <v>325.069838267509</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36746,28 +36831,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1114473021224731</v>
+        <v>-0.1098041676638907</v>
       </c>
       <c r="J8" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001713720683910402</v>
+        <v>0.00167212971594255</v>
       </c>
       <c r="M8" t="n">
-        <v>15.10671117110463</v>
+        <v>15.07584199424666</v>
       </c>
       <c r="N8" t="n">
-        <v>355.8599648960514</v>
+        <v>355.0240140972384</v>
       </c>
       <c r="O8" t="n">
-        <v>18.86425097627922</v>
+        <v>18.84208093861287</v>
       </c>
       <c r="P8" t="n">
-        <v>309.9922749838073</v>
+        <v>309.9731033067077</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36824,28 +36909,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7193746141240127</v>
+        <v>-0.714277007556309</v>
       </c>
       <c r="J9" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K9" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02771821060345414</v>
+        <v>0.02746869291787835</v>
       </c>
       <c r="M9" t="n">
-        <v>25.08718967668495</v>
+        <v>25.05021005069874</v>
       </c>
       <c r="N9" t="n">
-        <v>904.9375455856073</v>
+        <v>902.9578146923028</v>
       </c>
       <c r="O9" t="n">
-        <v>30.08217986758286</v>
+        <v>30.04925647486644</v>
       </c>
       <c r="P9" t="n">
-        <v>302.1142514569767</v>
+        <v>302.0551379440494</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36902,28 +36987,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6339540259028766</v>
+        <v>-0.6340702855700064</v>
       </c>
       <c r="J10" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K10" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01745651250158031</v>
+        <v>0.01755208262200825</v>
       </c>
       <c r="M10" t="n">
-        <v>27.98985427244529</v>
+        <v>27.92247783733353</v>
       </c>
       <c r="N10" t="n">
-        <v>1113.767055573212</v>
+        <v>1111.0638657124</v>
       </c>
       <c r="O10" t="n">
-        <v>33.37314872128808</v>
+        <v>33.33262464481907</v>
       </c>
       <c r="P10" t="n">
-        <v>293.1258857298589</v>
+        <v>293.1272407224399</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36980,28 +37065,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2866930077220538</v>
+        <v>-0.2877100225306879</v>
       </c>
       <c r="J11" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K11" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01137484924803811</v>
+        <v>0.01151397629818673</v>
       </c>
       <c r="M11" t="n">
-        <v>15.57519493866271</v>
+        <v>15.54206387118765</v>
       </c>
       <c r="N11" t="n">
-        <v>351.5653757740549</v>
+        <v>350.7155129153826</v>
       </c>
       <c r="O11" t="n">
-        <v>18.75007668715131</v>
+        <v>18.72740005754623</v>
       </c>
       <c r="P11" t="n">
-        <v>295.5513775537433</v>
+        <v>295.5632264078133</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37058,28 +37143,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.323513321261383</v>
+        <v>-0.3233796224708888</v>
       </c>
       <c r="J12" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K12" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01113064925298757</v>
+        <v>0.01117909412037676</v>
       </c>
       <c r="M12" t="n">
-        <v>17.96817282594228</v>
+        <v>17.92495511395435</v>
       </c>
       <c r="N12" t="n">
-        <v>462.0067860993946</v>
+        <v>460.8801104893334</v>
       </c>
       <c r="O12" t="n">
-        <v>21.49434311858342</v>
+        <v>21.46811846644539</v>
       </c>
       <c r="P12" t="n">
-        <v>296.5970523258615</v>
+        <v>296.5955035226898</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37136,28 +37221,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4410500015768719</v>
+        <v>0.4449611011973784</v>
       </c>
       <c r="J13" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K13" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0466304150719008</v>
+        <v>0.04762230313039073</v>
       </c>
       <c r="M13" t="n">
-        <v>11.28395861430189</v>
+        <v>11.27641051290209</v>
       </c>
       <c r="N13" t="n">
-        <v>194.5702444169473</v>
+        <v>194.2482418252254</v>
       </c>
       <c r="O13" t="n">
-        <v>13.94884383800132</v>
+        <v>13.93729679045493</v>
       </c>
       <c r="P13" t="n">
-        <v>300.3417111573935</v>
+        <v>300.2960405455118</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37214,28 +37299,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3434481209667966</v>
+        <v>0.3484513775164911</v>
       </c>
       <c r="J14" t="n">
+        <v>417</v>
+      </c>
+      <c r="K14" t="n">
         <v>416</v>
       </c>
-      <c r="K14" t="n">
-        <v>415</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02518153038691029</v>
+        <v>0.0260056173550588</v>
       </c>
       <c r="M14" t="n">
-        <v>11.77858086504592</v>
+        <v>11.77312397322672</v>
       </c>
       <c r="N14" t="n">
-        <v>223.890359798939</v>
+        <v>223.5890467894696</v>
       </c>
       <c r="O14" t="n">
-        <v>14.96296627674269</v>
+        <v>14.95289426129502</v>
       </c>
       <c r="P14" t="n">
-        <v>301.8603974120419</v>
+        <v>301.802038995794</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37292,28 +37377,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.001692969036524355</v>
+        <v>0.01151411875232105</v>
       </c>
       <c r="J15" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K15" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L15" t="n">
-        <v>4.159929506419857e-07</v>
+        <v>1.924774781270067e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>14.42446150309362</v>
+        <v>14.45041650364988</v>
       </c>
       <c r="N15" t="n">
-        <v>339.3155921264712</v>
+        <v>340.1500951960289</v>
       </c>
       <c r="O15" t="n">
-        <v>18.42052095154942</v>
+        <v>18.44315849294878</v>
       </c>
       <c r="P15" t="n">
-        <v>293.2567619936318</v>
+        <v>293.1030618640718</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37370,28 +37455,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03069483400502446</v>
+        <v>0.03438938229541263</v>
       </c>
       <c r="J16" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K16" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0002644106592620821</v>
+        <v>0.0003333407773919994</v>
       </c>
       <c r="M16" t="n">
-        <v>9.863909962919209</v>
+        <v>9.855984647677666</v>
       </c>
       <c r="N16" t="n">
-        <v>173.8970851968647</v>
+        <v>173.6060191761424</v>
       </c>
       <c r="O16" t="n">
-        <v>13.18700440573464</v>
+        <v>13.17596369060504</v>
       </c>
       <c r="P16" t="n">
-        <v>315.0310336733286</v>
+        <v>314.9877388152279</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37448,28 +37533,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04323848929668112</v>
+        <v>0.04871081845820989</v>
       </c>
       <c r="J17" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K17" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0007284529295505937</v>
+        <v>0.0009270263921655753</v>
       </c>
       <c r="M17" t="n">
-        <v>8.500667557859368</v>
+        <v>8.508886963611321</v>
       </c>
       <c r="N17" t="n">
-        <v>125.4676628248652</v>
+        <v>125.4498506486681</v>
       </c>
       <c r="O17" t="n">
-        <v>11.20123487946151</v>
+        <v>11.20043975246812</v>
       </c>
       <c r="P17" t="n">
-        <v>324.0137436902314</v>
+        <v>323.9498423209298</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37526,28 +37611,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02390508889605967</v>
+        <v>-0.01892710121576555</v>
       </c>
       <c r="J18" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K18" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0002895063964494238</v>
+        <v>0.0001820039885953584</v>
       </c>
       <c r="M18" t="n">
-        <v>7.451739351734799</v>
+        <v>7.459014626335931</v>
       </c>
       <c r="N18" t="n">
-        <v>96.44182375809648</v>
+        <v>96.44375666218697</v>
       </c>
       <c r="O18" t="n">
-        <v>9.820479813028307</v>
+        <v>9.82057822443195</v>
       </c>
       <c r="P18" t="n">
-        <v>330.2025874493947</v>
+        <v>330.144335575281</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37604,28 +37689,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.136406014718027</v>
+        <v>-0.1296880180991748</v>
       </c>
       <c r="J19" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K19" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007066269150455051</v>
+        <v>0.006403409829432549</v>
       </c>
       <c r="M19" t="n">
-        <v>8.83976808587628</v>
+        <v>8.847238113851374</v>
       </c>
       <c r="N19" t="n">
-        <v>127.9104088910021</v>
+        <v>128.0302765486075</v>
       </c>
       <c r="O19" t="n">
-        <v>11.30974840087091</v>
+        <v>11.31504646692215</v>
       </c>
       <c r="P19" t="n">
-        <v>344.9715968225319</v>
+        <v>344.8931495708706</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37682,28 +37767,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1445222770315993</v>
+        <v>0.1467789548300554</v>
       </c>
       <c r="J20" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K20" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00782677326064285</v>
+        <v>0.008109672061900497</v>
       </c>
       <c r="M20" t="n">
-        <v>8.40955370893626</v>
+        <v>8.398886799024055</v>
       </c>
       <c r="N20" t="n">
-        <v>129.5337979227804</v>
+        <v>129.2713032847167</v>
       </c>
       <c r="O20" t="n">
-        <v>11.38129157533452</v>
+        <v>11.3697538796896</v>
       </c>
       <c r="P20" t="n">
-        <v>340.9533020943684</v>
+        <v>340.9269504628899</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37760,28 +37845,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3185347127328282</v>
+        <v>-0.3170389925773482</v>
       </c>
       <c r="J21" t="n">
+        <v>417</v>
+      </c>
+      <c r="K21" t="n">
         <v>416</v>
       </c>
-      <c r="K21" t="n">
-        <v>415</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03175047929826857</v>
+        <v>0.03161618865231175</v>
       </c>
       <c r="M21" t="n">
-        <v>9.084601045996351</v>
+        <v>9.069001940861174</v>
       </c>
       <c r="N21" t="n">
-        <v>151.0871803666553</v>
+        <v>150.74509797473</v>
       </c>
       <c r="O21" t="n">
-        <v>12.29175253438887</v>
+        <v>12.27782953028466</v>
       </c>
       <c r="P21" t="n">
-        <v>347.9771853589511</v>
+        <v>347.9596878237667</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37838,28 +37923,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1117465477862035</v>
+        <v>-0.1437077294851834</v>
       </c>
       <c r="J22" t="n">
+        <v>417</v>
+      </c>
+      <c r="K22" t="n">
         <v>416</v>
       </c>
-      <c r="K22" t="n">
-        <v>415</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.003437985113865727</v>
+        <v>0.005512957202853608</v>
       </c>
       <c r="M22" t="n">
-        <v>9.474457116970491</v>
+        <v>9.630276255003416</v>
       </c>
       <c r="N22" t="n">
-        <v>176.7443930507174</v>
+        <v>182.4125006429797</v>
       </c>
       <c r="O22" t="n">
-        <v>13.29452492760525</v>
+        <v>13.50601720134325</v>
       </c>
       <c r="P22" t="n">
-        <v>337.3530640699848</v>
+        <v>337.7265255337595</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37897,7 +37982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W417"/>
+  <dimension ref="A1:W418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86221,17 +86306,17 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>-37.68484072692841,174.8114449674941</t>
+          <t>-37.684780039497596,174.81163618010802</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>-37.68416354635064,174.8111654745424</t>
+          <t>-37.68412187410588,174.8112967742344</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>-37.68346046118529,174.81096758189807</t>
+          <t>-37.68342132882084,174.81109087826974</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -86316,12 +86401,129 @@
       </c>
       <c r="V417" t="inlineStr">
         <is>
-          <t>-37.672106998299185,174.80570496192706</t>
+          <t>-37.67203967440074,174.80587629492337</t>
         </is>
       </c>
       <c r="W417" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-37.685478969378394,174.8118471274738</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-37.68477372344251,174.8116560805212</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-37.68413834919645,174.811244865072</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-37.68342467061607,174.81108034912285</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-37.68269290741286,174.81097279262835</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-37.68208919551326,174.8104617625455</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-37.681415587709736,174.8101735667593</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-37.68069609015102,174.81003691977776</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-37.679976149563494,174.80990177926816</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-37.679343077624054,174.80948095756196</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-37.67868511318554,174.80914052967384</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-37.67812318681744,174.80848983871473</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-37.677461121959354,174.80816261883308</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-37.67679617358506,174.80786549315033</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-37.676143983416104,174.80754363556588</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-37.67550323986382,174.8071453645096</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-37.67483204670844,174.8068480631138</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>-37.674193171532536,174.8064223735694</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>-37.67349631931727,174.80621943784533</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>-37.672797175701554,174.80599033533514</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>-37.67192954380126,174.80615656494112</t>
+        </is>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
